--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/General.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/General.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15835" uniqueCount="10486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15841" uniqueCount="10491">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -27398,6 +27398,21 @@
   </si>
   <si>
     <t xml:space="preserve">バックパックのベッドを使う</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hotActionBinocular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">백팩 안의 쌍안경을 사용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use binocular in inventory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">バックパックの双眼鏡を使う</t>
   </si>
   <si>
     <t xml:space="preserve">updateEQ</t>
@@ -32127,14 +32142,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F2795"/>
+  <dimension ref="A1:F2796"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="16.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="43.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="27.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="16.15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -78797,24 +78808,24 @@
         <v>9033</v>
       </c>
       <c r="B2424" s="0" t="s">
-        <v>148</v>
+        <v>9034</v>
       </c>
       <c r="C2424" s="0" t="s">
         <v>3953</v>
       </c>
       <c r="D2424" s="0" t="s">
-        <v>9034</v>
+        <v>9035</v>
       </c>
       <c r="E2424" s="0" t="s">
-        <v>9035</v>
+        <v>9036</v>
       </c>
       <c r="F2424" s="0" t="s">
-        <v>9036</v>
+        <v>9037</v>
       </c>
     </row>
     <row r="2425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2425" s="0" t="s">
-        <v>9037</v>
+        <v>9038</v>
       </c>
       <c r="B2425" s="0" t="s">
         <v>148</v>
@@ -78823,18 +78834,18 @@
         <v>3953</v>
       </c>
       <c r="D2425" s="0" t="s">
-        <v>9038</v>
+        <v>9039</v>
       </c>
       <c r="E2425" s="0" t="s">
-        <v>9039</v>
+        <v>9040</v>
       </c>
       <c r="F2425" s="0" t="s">
-        <v>9040</v>
+        <v>9041</v>
       </c>
     </row>
     <row r="2426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2426" s="0" t="s">
-        <v>9041</v>
+        <v>9042</v>
       </c>
       <c r="B2426" s="0" t="s">
         <v>148</v>
@@ -78843,38 +78854,38 @@
         <v>3953</v>
       </c>
       <c r="D2426" s="0" t="s">
-        <v>9042</v>
+        <v>9043</v>
       </c>
       <c r="E2426" s="0" t="s">
-        <v>9043</v>
+        <v>9044</v>
       </c>
       <c r="F2426" s="0" t="s">
-        <v>9044</v>
+        <v>9045</v>
       </c>
     </row>
     <row r="2427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2427" s="0" t="s">
-        <v>9045</v>
+        <v>9046</v>
       </c>
       <c r="B2427" s="0" t="s">
-        <v>4716</v>
+        <v>148</v>
       </c>
       <c r="C2427" s="0" t="s">
         <v>3953</v>
       </c>
       <c r="D2427" s="0" t="s">
-        <v>9046</v>
+        <v>9047</v>
       </c>
       <c r="E2427" s="0" t="s">
-        <v>9047</v>
+        <v>9048</v>
       </c>
       <c r="F2427" s="0" t="s">
-        <v>9048</v>
+        <v>9049</v>
       </c>
     </row>
     <row r="2428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2428" s="0" t="s">
-        <v>9049</v>
+        <v>9050</v>
       </c>
       <c r="B2428" s="0" t="s">
         <v>4716</v>
@@ -78883,18 +78894,18 @@
         <v>3953</v>
       </c>
       <c r="D2428" s="0" t="s">
-        <v>9050</v>
+        <v>9051</v>
       </c>
       <c r="E2428" s="0" t="s">
-        <v>9051</v>
+        <v>9052</v>
       </c>
       <c r="F2428" s="0" t="s">
-        <v>9052</v>
+        <v>9053</v>
       </c>
     </row>
     <row r="2429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2429" s="0" t="s">
-        <v>9053</v>
+        <v>9054</v>
       </c>
       <c r="B2429" s="0" t="s">
         <v>4716</v>
@@ -78903,78 +78914,78 @@
         <v>3953</v>
       </c>
       <c r="D2429" s="0" t="s">
-        <v>9054</v>
+        <v>9055</v>
       </c>
       <c r="E2429" s="0" t="s">
-        <v>9055</v>
+        <v>9056</v>
       </c>
       <c r="F2429" s="0" t="s">
-        <v>9056</v>
+        <v>9057</v>
       </c>
     </row>
     <row r="2430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2430" s="0" t="s">
-        <v>9057</v>
+        <v>9058</v>
       </c>
       <c r="B2430" s="0" t="s">
-        <v>191</v>
+        <v>4716</v>
       </c>
       <c r="C2430" s="0" t="s">
-        <v>6141</v>
+        <v>3953</v>
       </c>
       <c r="D2430" s="0" t="s">
-        <v>9058</v>
+        <v>9059</v>
       </c>
       <c r="E2430" s="0" t="s">
-        <v>9059</v>
+        <v>9060</v>
       </c>
       <c r="F2430" s="0" t="s">
-        <v>9060</v>
+        <v>9061</v>
       </c>
     </row>
     <row r="2431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2431" s="0" t="s">
-        <v>9061</v>
+        <v>9062</v>
       </c>
       <c r="B2431" s="0" t="s">
         <v>191</v>
       </c>
       <c r="C2431" s="0" t="s">
+        <v>6141</v>
+      </c>
+      <c r="D2431" s="0" t="s">
+        <v>9063</v>
+      </c>
+      <c r="E2431" s="0" t="s">
+        <v>9064</v>
+      </c>
+      <c r="F2431" s="0" t="s">
+        <v>9065</v>
+      </c>
+    </row>
+    <row r="2432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2432" s="0" t="s">
+        <v>9066</v>
+      </c>
+      <c r="B2432" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2432" s="0" t="s">
         <v>4800</v>
       </c>
-      <c r="D2431" s="0" t="s">
-        <v>9062</v>
-      </c>
-      <c r="E2431" s="0" t="s">
-        <v>9063</v>
-      </c>
-      <c r="F2431" s="0" t="s">
-        <v>9064</v>
-      </c>
-    </row>
-    <row r="2432" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2432" s="0" t="s">
-        <v>9065</v>
-      </c>
-      <c r="B2432" s="0" t="s">
-        <v>1828</v>
-      </c>
-      <c r="C2432" s="0" t="s">
-        <v>3283</v>
-      </c>
-      <c r="D2432" s="2" t="s">
-        <v>9066</v>
-      </c>
-      <c r="E2432" s="2" t="s">
+      <c r="D2432" s="0" t="s">
         <v>9067</v>
       </c>
-      <c r="F2432" s="2" t="s">
+      <c r="E2432" s="0" t="s">
         <v>9068</v>
+      </c>
+      <c r="F2432" s="0" t="s">
+        <v>9069</v>
       </c>
     </row>
     <row r="2433" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2433" s="0" t="s">
-        <v>9069</v>
+        <v>9070</v>
       </c>
       <c r="B2433" s="0" t="s">
         <v>1828</v>
@@ -78983,18 +78994,18 @@
         <v>3283</v>
       </c>
       <c r="D2433" s="2" t="s">
-        <v>9070</v>
+        <v>9071</v>
       </c>
       <c r="E2433" s="2" t="s">
-        <v>9071</v>
+        <v>9072</v>
       </c>
       <c r="F2433" s="2" t="s">
-        <v>9072</v>
-      </c>
-    </row>
-    <row r="2434" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>9073</v>
+      </c>
+    </row>
+    <row r="2434" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2434" s="0" t="s">
-        <v>9073</v>
+        <v>9074</v>
       </c>
       <c r="B2434" s="0" t="s">
         <v>1828</v>
@@ -79003,140 +79014,140 @@
         <v>3283</v>
       </c>
       <c r="D2434" s="2" t="s">
-        <v>9074</v>
+        <v>9075</v>
       </c>
       <c r="E2434" s="2" t="s">
-        <v>9075</v>
+        <v>9076</v>
       </c>
       <c r="F2434" s="2" t="s">
-        <v>9076</v>
-      </c>
-    </row>
-    <row r="2435" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>9077</v>
+      </c>
+    </row>
+    <row r="2435" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2435" s="0" t="s">
-        <v>9077</v>
+        <v>9078</v>
       </c>
       <c r="B2435" s="0" t="s">
-        <v>624</v>
-      </c>
-      <c r="D2435" s="0" t="s">
-        <v>9078</v>
-      </c>
-      <c r="E2435" s="0" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C2435" s="0" t="s">
+        <v>3283</v>
+      </c>
+      <c r="D2435" s="2" t="s">
         <v>9079</v>
       </c>
-      <c r="F2435" s="0" t="s">
+      <c r="E2435" s="2" t="s">
         <v>9080</v>
+      </c>
+      <c r="F2435" s="2" t="s">
+        <v>9081</v>
       </c>
     </row>
     <row r="2436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2436" s="0" t="s">
-        <v>9081</v>
+        <v>9082</v>
       </c>
       <c r="B2436" s="0" t="s">
         <v>624</v>
       </c>
       <c r="D2436" s="0" t="s">
-        <v>9082</v>
+        <v>9083</v>
       </c>
       <c r="E2436" s="0" t="s">
-        <v>9083</v>
+        <v>9084</v>
       </c>
       <c r="F2436" s="0" t="s">
-        <v>9084</v>
+        <v>9085</v>
       </c>
     </row>
     <row r="2437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2437" s="0" t="s">
-        <v>9085</v>
+        <v>9086</v>
       </c>
       <c r="B2437" s="0" t="s">
-        <v>2244</v>
+        <v>624</v>
       </c>
       <c r="D2437" s="0" t="s">
-        <v>9086</v>
+        <v>9087</v>
       </c>
       <c r="E2437" s="0" t="s">
-        <v>9087</v>
+        <v>9088</v>
       </c>
       <c r="F2437" s="0" t="s">
-        <v>9088</v>
+        <v>9089</v>
       </c>
     </row>
     <row r="2438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2438" s="0" t="s">
-        <v>9089</v>
+        <v>9090</v>
       </c>
       <c r="B2438" s="0" t="s">
         <v>2244</v>
       </c>
       <c r="D2438" s="0" t="s">
-        <v>9090</v>
+        <v>9091</v>
       </c>
       <c r="E2438" s="0" t="s">
-        <v>9091</v>
+        <v>9092</v>
       </c>
       <c r="F2438" s="0" t="s">
-        <v>9092</v>
+        <v>9093</v>
       </c>
     </row>
     <row r="2439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2439" s="0" t="s">
-        <v>9093</v>
+        <v>9094</v>
       </c>
       <c r="B2439" s="0" t="s">
-        <v>747</v>
+        <v>2244</v>
       </c>
       <c r="D2439" s="0" t="s">
-        <v>9094</v>
+        <v>9095</v>
       </c>
       <c r="E2439" s="0" t="s">
-        <v>9095</v>
+        <v>9096</v>
       </c>
       <c r="F2439" s="0" t="s">
-        <v>9096</v>
+        <v>9097</v>
       </c>
     </row>
     <row r="2440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2440" s="0" t="s">
-        <v>9097</v>
+        <v>9098</v>
       </c>
       <c r="B2440" s="0" t="s">
-        <v>45</v>
+        <v>747</v>
       </c>
       <c r="D2440" s="0" t="s">
-        <v>9098</v>
+        <v>9099</v>
       </c>
       <c r="E2440" s="0" t="s">
-        <v>9099</v>
+        <v>9100</v>
       </c>
       <c r="F2440" s="0" t="s">
-        <v>9100</v>
+        <v>9101</v>
       </c>
     </row>
     <row r="2441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2441" s="0" t="s">
-        <v>9101</v>
+        <v>9102</v>
       </c>
       <c r="B2441" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="C2441" s="0" t="s">
-        <v>990</v>
+        <v>45</v>
       </c>
       <c r="D2441" s="0" t="s">
-        <v>9102</v>
+        <v>9103</v>
       </c>
       <c r="E2441" s="0" t="s">
-        <v>9103</v>
+        <v>9104</v>
       </c>
       <c r="F2441" s="0" t="s">
-        <v>9104</v>
+        <v>9105</v>
       </c>
     </row>
     <row r="2442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2442" s="0" t="s">
-        <v>9105</v>
+        <v>9106</v>
       </c>
       <c r="B2442" s="0" t="s">
         <v>583</v>
@@ -79145,18 +79156,18 @@
         <v>990</v>
       </c>
       <c r="D2442" s="0" t="s">
-        <v>9106</v>
+        <v>9107</v>
       </c>
       <c r="E2442" s="0" t="s">
-        <v>9107</v>
+        <v>9108</v>
       </c>
       <c r="F2442" s="0" t="s">
-        <v>9108</v>
+        <v>9109</v>
       </c>
     </row>
     <row r="2443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2443" s="0" t="s">
-        <v>9109</v>
+        <v>9110</v>
       </c>
       <c r="B2443" s="0" t="s">
         <v>583</v>
@@ -79165,18 +79176,18 @@
         <v>990</v>
       </c>
       <c r="D2443" s="0" t="s">
-        <v>9110</v>
+        <v>9111</v>
       </c>
       <c r="E2443" s="0" t="s">
-        <v>9111</v>
+        <v>9112</v>
       </c>
       <c r="F2443" s="0" t="s">
-        <v>9112</v>
+        <v>9113</v>
       </c>
     </row>
     <row r="2444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2444" s="0" t="s">
-        <v>9113</v>
+        <v>9114</v>
       </c>
       <c r="B2444" s="0" t="s">
         <v>583</v>
@@ -79185,18 +79196,18 @@
         <v>990</v>
       </c>
       <c r="D2444" s="0" t="s">
-        <v>9114</v>
+        <v>9115</v>
       </c>
       <c r="E2444" s="0" t="s">
-        <v>9115</v>
+        <v>9116</v>
       </c>
       <c r="F2444" s="0" t="s">
-        <v>9116</v>
+        <v>9117</v>
       </c>
     </row>
     <row r="2445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2445" s="0" t="s">
-        <v>9117</v>
+        <v>9118</v>
       </c>
       <c r="B2445" s="0" t="s">
         <v>583</v>
@@ -79205,24 +79216,24 @@
         <v>990</v>
       </c>
       <c r="D2445" s="0" t="s">
-        <v>9118</v>
+        <v>9119</v>
       </c>
       <c r="E2445" s="0" t="s">
-        <v>9119</v>
+        <v>9120</v>
       </c>
       <c r="F2445" s="0" t="s">
-        <v>9120</v>
+        <v>9121</v>
       </c>
     </row>
     <row r="2446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2446" s="0" t="s">
-        <v>9121</v>
+        <v>9122</v>
       </c>
       <c r="B2446" s="0" t="s">
-        <v>391</v>
+        <v>583</v>
       </c>
       <c r="C2446" s="0" t="s">
-        <v>9122</v>
+        <v>990</v>
       </c>
       <c r="D2446" s="0" t="s">
         <v>9123</v>
@@ -79239,10 +79250,10 @@
         <v>9126</v>
       </c>
       <c r="B2447" s="0" t="s">
+        <v>391</v>
+      </c>
+      <c r="C2447" s="0" t="s">
         <v>9127</v>
-      </c>
-      <c r="C2447" s="0" t="s">
-        <v>9122</v>
       </c>
       <c r="D2447" s="0" t="s">
         <v>9128</v>
@@ -79259,555 +79270,558 @@
         <v>9131</v>
       </c>
       <c r="B2448" s="0" t="s">
-        <v>583</v>
+        <v>9132</v>
       </c>
       <c r="C2448" s="0" t="s">
-        <v>9122</v>
+        <v>9127</v>
       </c>
       <c r="D2448" s="0" t="s">
-        <v>9132</v>
+        <v>9133</v>
       </c>
       <c r="E2448" s="0" t="s">
-        <v>9133</v>
+        <v>9134</v>
       </c>
       <c r="F2448" s="0" t="s">
-        <v>9134</v>
+        <v>9135</v>
       </c>
     </row>
     <row r="2449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2449" s="0" t="s">
-        <v>9135</v>
+        <v>9136</v>
       </c>
       <c r="B2449" s="0" t="s">
         <v>583</v>
       </c>
       <c r="C2449" s="0" t="s">
-        <v>9122</v>
+        <v>9127</v>
       </c>
       <c r="D2449" s="0" t="s">
-        <v>9136</v>
+        <v>9137</v>
       </c>
       <c r="E2449" s="0" t="s">
-        <v>9137</v>
+        <v>9138</v>
       </c>
       <c r="F2449" s="0" t="s">
-        <v>9138</v>
+        <v>9139</v>
       </c>
     </row>
     <row r="2450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2450" s="0" t="s">
-        <v>9139</v>
+        <v>9140</v>
       </c>
       <c r="B2450" s="0" t="s">
         <v>583</v>
       </c>
       <c r="C2450" s="0" t="s">
-        <v>9122</v>
+        <v>9127</v>
       </c>
       <c r="D2450" s="0" t="s">
-        <v>9140</v>
+        <v>9141</v>
       </c>
       <c r="E2450" s="0" t="s">
-        <v>9141</v>
+        <v>9142</v>
       </c>
       <c r="F2450" s="0" t="s">
-        <v>9142</v>
+        <v>9143</v>
       </c>
     </row>
     <row r="2451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2451" s="0" t="s">
-        <v>9143</v>
+        <v>9144</v>
       </c>
       <c r="B2451" s="0" t="s">
-        <v>45</v>
+        <v>583</v>
       </c>
       <c r="C2451" s="0" t="s">
-        <v>9122</v>
+        <v>9127</v>
       </c>
       <c r="D2451" s="0" t="s">
-        <v>9144</v>
+        <v>9145</v>
       </c>
       <c r="E2451" s="0" t="s">
-        <v>9145</v>
+        <v>9146</v>
       </c>
       <c r="F2451" s="0" t="s">
-        <v>9146</v>
+        <v>9147</v>
       </c>
     </row>
     <row r="2452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2452" s="0" t="s">
-        <v>9147</v>
+        <v>9148</v>
       </c>
       <c r="B2452" s="0" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="C2452" s="0" t="s">
-        <v>9122</v>
+        <v>9127</v>
       </c>
       <c r="D2452" s="0" t="s">
-        <v>9148</v>
+        <v>9149</v>
       </c>
       <c r="E2452" s="0" t="s">
-        <v>9149</v>
+        <v>9150</v>
       </c>
       <c r="F2452" s="0" t="s">
-        <v>9150</v>
+        <v>9151</v>
       </c>
     </row>
     <row r="2453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2453" s="0" t="s">
-        <v>9151</v>
+        <v>9152</v>
       </c>
       <c r="B2453" s="0" t="s">
         <v>118</v>
       </c>
       <c r="C2453" s="0" t="s">
-        <v>9122</v>
+        <v>9127</v>
       </c>
       <c r="D2453" s="0" t="s">
-        <v>9152</v>
+        <v>9153</v>
       </c>
       <c r="E2453" s="0" t="s">
-        <v>9153</v>
+        <v>9154</v>
       </c>
       <c r="F2453" s="0" t="s">
-        <v>9154</v>
+        <v>9155</v>
       </c>
     </row>
     <row r="2454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2454" s="0" t="s">
-        <v>9155</v>
+        <v>9156</v>
       </c>
       <c r="B2454" s="0" t="s">
         <v>118</v>
       </c>
       <c r="C2454" s="0" t="s">
-        <v>9122</v>
+        <v>9127</v>
       </c>
       <c r="D2454" s="0" t="s">
-        <v>9156</v>
+        <v>9157</v>
       </c>
       <c r="E2454" s="0" t="s">
-        <v>9157</v>
+        <v>9158</v>
       </c>
       <c r="F2454" s="0" t="s">
-        <v>9158</v>
+        <v>9159</v>
       </c>
     </row>
     <row r="2455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2455" s="0" t="s">
-        <v>9159</v>
+        <v>9160</v>
       </c>
       <c r="B2455" s="0" t="s">
-        <v>2893</v>
+        <v>118</v>
+      </c>
+      <c r="C2455" s="0" t="s">
+        <v>9127</v>
       </c>
       <c r="D2455" s="0" t="s">
-        <v>9160</v>
+        <v>9161</v>
       </c>
       <c r="E2455" s="0" t="s">
-        <v>9161</v>
+        <v>9162</v>
       </c>
       <c r="F2455" s="0" t="s">
-        <v>9162</v>
+        <v>9163</v>
       </c>
     </row>
     <row r="2456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2456" s="0" t="s">
-        <v>9163</v>
+        <v>9164</v>
       </c>
       <c r="B2456" s="0" t="s">
-        <v>4420</v>
+        <v>2893</v>
       </c>
       <c r="D2456" s="0" t="s">
-        <v>9164</v>
+        <v>9165</v>
       </c>
       <c r="E2456" s="0" t="s">
-        <v>9165</v>
+        <v>9166</v>
       </c>
       <c r="F2456" s="0" t="s">
-        <v>9166</v>
+        <v>9167</v>
       </c>
     </row>
     <row r="2457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2457" s="0" t="s">
-        <v>9167</v>
+        <v>9168</v>
       </c>
       <c r="B2457" s="0" t="s">
         <v>4420</v>
       </c>
       <c r="D2457" s="0" t="s">
-        <v>9168</v>
+        <v>9169</v>
       </c>
       <c r="E2457" s="0" t="s">
-        <v>9169</v>
+        <v>9170</v>
       </c>
       <c r="F2457" s="0" t="s">
-        <v>9170</v>
+        <v>9171</v>
       </c>
     </row>
     <row r="2458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2458" s="0" t="s">
-        <v>9171</v>
+        <v>9172</v>
       </c>
       <c r="B2458" s="0" t="s">
         <v>4420</v>
       </c>
       <c r="D2458" s="0" t="s">
-        <v>9172</v>
+        <v>9173</v>
       </c>
       <c r="E2458" s="0" t="s">
-        <v>9173</v>
+        <v>9174</v>
       </c>
       <c r="F2458" s="0" t="s">
-        <v>9174</v>
+        <v>9175</v>
       </c>
     </row>
     <row r="2459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2459" s="0" t="s">
-        <v>9175</v>
+        <v>9176</v>
       </c>
       <c r="B2459" s="0" t="s">
         <v>4420</v>
       </c>
       <c r="D2459" s="0" t="s">
-        <v>9176</v>
+        <v>9177</v>
       </c>
       <c r="E2459" s="0" t="s">
-        <v>9177</v>
+        <v>9178</v>
       </c>
       <c r="F2459" s="0" t="s">
-        <v>9178</v>
+        <v>9179</v>
       </c>
     </row>
     <row r="2460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2460" s="0" t="s">
-        <v>9179</v>
+        <v>9180</v>
       </c>
       <c r="B2460" s="0" t="s">
-        <v>118</v>
+        <v>4420</v>
       </c>
       <c r="D2460" s="0" t="s">
-        <v>9180</v>
+        <v>9181</v>
       </c>
       <c r="E2460" s="0" t="s">
-        <v>9181</v>
+        <v>9182</v>
       </c>
       <c r="F2460" s="0" t="s">
-        <v>9182</v>
+        <v>9183</v>
       </c>
     </row>
     <row r="2461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2461" s="0" t="s">
-        <v>9183</v>
+        <v>9184</v>
       </c>
       <c r="B2461" s="0" t="s">
         <v>118</v>
       </c>
       <c r="D2461" s="0" t="s">
-        <v>9184</v>
+        <v>9185</v>
       </c>
       <c r="E2461" s="0" t="s">
-        <v>9185</v>
+        <v>9186</v>
       </c>
       <c r="F2461" s="0" t="s">
-        <v>9186</v>
+        <v>9187</v>
       </c>
     </row>
     <row r="2462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2462" s="0" t="s">
-        <v>9187</v>
+        <v>9188</v>
       </c>
       <c r="B2462" s="0" t="s">
         <v>118</v>
       </c>
       <c r="D2462" s="0" t="s">
-        <v>9188</v>
+        <v>9189</v>
       </c>
       <c r="E2462" s="0" t="s">
-        <v>9189</v>
+        <v>9190</v>
       </c>
       <c r="F2462" s="0" t="s">
-        <v>9190</v>
+        <v>9191</v>
       </c>
     </row>
     <row r="2463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2463" s="0" t="s">
-        <v>9191</v>
+        <v>9192</v>
       </c>
       <c r="B2463" s="0" t="s">
         <v>118</v>
       </c>
       <c r="D2463" s="0" t="s">
-        <v>9192</v>
+        <v>9193</v>
       </c>
       <c r="E2463" s="0" t="s">
-        <v>9193</v>
+        <v>9194</v>
       </c>
       <c r="F2463" s="0" t="s">
-        <v>9194</v>
+        <v>9195</v>
       </c>
     </row>
     <row r="2464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2464" s="0" t="s">
-        <v>9195</v>
+        <v>9196</v>
       </c>
       <c r="B2464" s="0" t="s">
         <v>118</v>
       </c>
       <c r="D2464" s="0" t="s">
-        <v>9196</v>
+        <v>9197</v>
       </c>
       <c r="E2464" s="0" t="s">
-        <v>9197</v>
+        <v>9198</v>
       </c>
       <c r="F2464" s="0" t="s">
-        <v>9198</v>
+        <v>9199</v>
       </c>
     </row>
     <row r="2465" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2465" s="0" t="s">
-        <v>9199</v>
+        <v>9200</v>
       </c>
       <c r="B2465" s="0" t="s">
         <v>118</v>
       </c>
       <c r="D2465" s="0" t="s">
-        <v>9200</v>
+        <v>9201</v>
       </c>
       <c r="E2465" s="0" t="s">
-        <v>9201</v>
+        <v>9202</v>
       </c>
       <c r="F2465" s="0" t="s">
-        <v>9202</v>
+        <v>9203</v>
       </c>
     </row>
     <row r="2466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2466" s="0" t="s">
-        <v>9203</v>
+        <v>9204</v>
       </c>
       <c r="B2466" s="0" t="s">
         <v>118</v>
       </c>
       <c r="D2466" s="0" t="s">
-        <v>9204</v>
+        <v>9205</v>
       </c>
       <c r="E2466" s="0" t="s">
-        <v>9205</v>
+        <v>9206</v>
       </c>
       <c r="F2466" s="0" t="s">
-        <v>9206</v>
+        <v>9207</v>
       </c>
     </row>
     <row r="2467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2467" s="0" t="s">
-        <v>9207</v>
+        <v>9208</v>
       </c>
       <c r="B2467" s="0" t="s">
         <v>118</v>
       </c>
       <c r="D2467" s="0" t="s">
-        <v>9208</v>
+        <v>9209</v>
       </c>
       <c r="E2467" s="0" t="s">
-        <v>9209</v>
+        <v>9210</v>
       </c>
       <c r="F2467" s="0" t="s">
-        <v>9210</v>
+        <v>9211</v>
       </c>
     </row>
     <row r="2468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2468" s="0" t="s">
-        <v>9211</v>
+        <v>9212</v>
       </c>
       <c r="B2468" s="0" t="s">
         <v>118</v>
       </c>
       <c r="D2468" s="0" t="s">
-        <v>9212</v>
+        <v>9213</v>
       </c>
       <c r="E2468" s="0" t="s">
-        <v>9213</v>
+        <v>9214</v>
       </c>
       <c r="F2468" s="0" t="s">
-        <v>9214</v>
+        <v>9215</v>
       </c>
     </row>
     <row r="2469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2469" s="0" t="s">
-        <v>9215</v>
+        <v>9216</v>
       </c>
       <c r="B2469" s="0" t="s">
         <v>118</v>
       </c>
       <c r="D2469" s="0" t="s">
-        <v>9216</v>
+        <v>9217</v>
       </c>
       <c r="E2469" s="0" t="s">
-        <v>9217</v>
+        <v>9218</v>
       </c>
       <c r="F2469" s="0" t="s">
-        <v>9218</v>
+        <v>9219</v>
       </c>
     </row>
     <row r="2470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2470" s="0" t="s">
-        <v>9219</v>
+        <v>9220</v>
       </c>
       <c r="B2470" s="0" t="s">
         <v>118</v>
       </c>
       <c r="D2470" s="0" t="s">
-        <v>9220</v>
+        <v>9221</v>
       </c>
       <c r="E2470" s="0" t="s">
-        <v>9221</v>
+        <v>9222</v>
       </c>
       <c r="F2470" s="0" t="s">
-        <v>9222</v>
+        <v>9223</v>
       </c>
     </row>
     <row r="2471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2471" s="0" t="s">
-        <v>9223</v>
+        <v>9224</v>
       </c>
       <c r="B2471" s="0" t="s">
         <v>118</v>
       </c>
       <c r="D2471" s="0" t="s">
-        <v>9224</v>
+        <v>9225</v>
       </c>
       <c r="E2471" s="0" t="s">
-        <v>9225</v>
+        <v>9226</v>
       </c>
       <c r="F2471" s="0" t="s">
-        <v>9226</v>
+        <v>9227</v>
       </c>
     </row>
     <row r="2472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2472" s="0" t="s">
-        <v>9227</v>
+        <v>9228</v>
       </c>
       <c r="B2472" s="0" t="s">
         <v>118</v>
       </c>
       <c r="D2472" s="0" t="s">
-        <v>9228</v>
+        <v>9229</v>
       </c>
       <c r="E2472" s="0" t="s">
-        <v>9229</v>
+        <v>9230</v>
       </c>
       <c r="F2472" s="0" t="s">
-        <v>9230</v>
+        <v>9231</v>
       </c>
     </row>
     <row r="2473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2473" s="0" t="s">
-        <v>9231</v>
+        <v>9232</v>
       </c>
       <c r="B2473" s="0" t="s">
         <v>118</v>
       </c>
       <c r="D2473" s="0" t="s">
-        <v>9232</v>
+        <v>9233</v>
       </c>
       <c r="E2473" s="0" t="s">
-        <v>9233</v>
+        <v>9234</v>
       </c>
       <c r="F2473" s="0" t="s">
-        <v>9234</v>
+        <v>9235</v>
       </c>
     </row>
     <row r="2474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2474" s="0" t="s">
-        <v>9235</v>
+        <v>9236</v>
       </c>
       <c r="B2474" s="0" t="s">
         <v>118</v>
       </c>
       <c r="D2474" s="0" t="s">
-        <v>9236</v>
+        <v>9237</v>
       </c>
       <c r="E2474" s="0" t="s">
-        <v>9237</v>
+        <v>9238</v>
       </c>
       <c r="F2474" s="0" t="s">
-        <v>9238</v>
+        <v>9239</v>
       </c>
     </row>
     <row r="2475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2475" s="0" t="s">
-        <v>9239</v>
+        <v>9240</v>
       </c>
       <c r="B2475" s="0" t="s">
         <v>118</v>
       </c>
       <c r="D2475" s="0" t="s">
-        <v>9240</v>
+        <v>9241</v>
       </c>
       <c r="E2475" s="0" t="s">
-        <v>9241</v>
+        <v>9242</v>
       </c>
       <c r="F2475" s="0" t="s">
-        <v>9242</v>
+        <v>9243</v>
       </c>
     </row>
     <row r="2476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2476" s="0" t="s">
-        <v>9243</v>
+        <v>9244</v>
       </c>
       <c r="B2476" s="0" t="s">
-        <v>1788</v>
+        <v>118</v>
       </c>
       <c r="D2476" s="0" t="s">
-        <v>9244</v>
+        <v>9245</v>
       </c>
       <c r="E2476" s="0" t="s">
-        <v>9245</v>
+        <v>9246</v>
       </c>
       <c r="F2476" s="0" t="s">
-        <v>9246</v>
+        <v>9247</v>
       </c>
     </row>
     <row r="2477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2477" s="0" t="s">
-        <v>9247</v>
+        <v>9248</v>
       </c>
       <c r="B2477" s="0" t="s">
-        <v>118</v>
+        <v>1788</v>
       </c>
       <c r="D2477" s="0" t="s">
-        <v>9248</v>
+        <v>9249</v>
       </c>
       <c r="E2477" s="0" t="s">
-        <v>9249</v>
+        <v>9250</v>
       </c>
       <c r="F2477" s="0" t="s">
-        <v>9250</v>
+        <v>9251</v>
       </c>
     </row>
     <row r="2478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2478" s="0" t="s">
-        <v>9251</v>
+        <v>9252</v>
       </c>
       <c r="B2478" s="0" t="s">
         <v>118</v>
       </c>
       <c r="D2478" s="0" t="s">
-        <v>9252</v>
+        <v>9253</v>
       </c>
       <c r="E2478" s="0" t="s">
-        <v>9253</v>
+        <v>9254</v>
       </c>
       <c r="F2478" s="0" t="s">
-        <v>9254</v>
+        <v>9255</v>
       </c>
     </row>
     <row r="2479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2479" s="0" t="s">
-        <v>9255</v>
+        <v>9256</v>
       </c>
       <c r="B2479" s="0" t="s">
-        <v>9256</v>
+        <v>118</v>
       </c>
       <c r="D2479" s="0" t="s">
         <v>9257</v>
@@ -79824,457 +79838,457 @@
         <v>9260</v>
       </c>
       <c r="B2480" s="0" t="s">
-        <v>9256</v>
+        <v>9261</v>
       </c>
       <c r="D2480" s="0" t="s">
-        <v>9261</v>
+        <v>9262</v>
       </c>
       <c r="E2480" s="0" t="s">
-        <v>9262</v>
+        <v>9263</v>
       </c>
       <c r="F2480" s="0" t="s">
-        <v>9263</v>
+        <v>9264</v>
       </c>
     </row>
     <row r="2481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2481" s="0" t="s">
-        <v>9264</v>
+        <v>9265</v>
       </c>
       <c r="B2481" s="0" t="s">
-        <v>9256</v>
+        <v>9261</v>
       </c>
       <c r="D2481" s="0" t="s">
-        <v>9265</v>
+        <v>9266</v>
       </c>
       <c r="E2481" s="0" t="s">
-        <v>9266</v>
+        <v>9267</v>
       </c>
       <c r="F2481" s="0" t="s">
-        <v>9267</v>
+        <v>9268</v>
       </c>
     </row>
     <row r="2482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2482" s="0" t="s">
-        <v>9268</v>
+        <v>9269</v>
       </c>
       <c r="B2482" s="0" t="s">
-        <v>9256</v>
+        <v>9261</v>
       </c>
       <c r="D2482" s="0" t="s">
-        <v>9269</v>
+        <v>9270</v>
       </c>
       <c r="E2482" s="0" t="s">
-        <v>9270</v>
+        <v>9271</v>
       </c>
       <c r="F2482" s="0" t="s">
-        <v>9271</v>
+        <v>9272</v>
       </c>
     </row>
     <row r="2483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2483" s="0" t="s">
-        <v>9272</v>
+        <v>9273</v>
       </c>
       <c r="B2483" s="0" t="s">
-        <v>554</v>
+        <v>9261</v>
       </c>
       <c r="D2483" s="0" t="s">
-        <v>9273</v>
+        <v>9274</v>
       </c>
       <c r="E2483" s="0" t="s">
-        <v>9274</v>
+        <v>9275</v>
       </c>
       <c r="F2483" s="0" t="s">
-        <v>9275</v>
+        <v>9276</v>
       </c>
     </row>
     <row r="2484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2484" s="0" t="s">
-        <v>9276</v>
+        <v>9277</v>
       </c>
       <c r="B2484" s="0" t="s">
-        <v>118</v>
+        <v>554</v>
       </c>
       <c r="D2484" s="0" t="s">
-        <v>9277</v>
+        <v>9278</v>
       </c>
       <c r="E2484" s="0" t="s">
-        <v>9278</v>
+        <v>9279</v>
       </c>
       <c r="F2484" s="0" t="s">
-        <v>9279</v>
+        <v>9280</v>
       </c>
     </row>
     <row r="2485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2485" s="0" t="s">
-        <v>9280</v>
+        <v>9281</v>
       </c>
       <c r="B2485" s="0" t="s">
         <v>118</v>
       </c>
       <c r="D2485" s="0" t="s">
-        <v>9281</v>
+        <v>9282</v>
       </c>
       <c r="E2485" s="0" t="s">
-        <v>9282</v>
+        <v>9283</v>
       </c>
       <c r="F2485" s="0" t="s">
-        <v>9283</v>
+        <v>9284</v>
       </c>
     </row>
     <row r="2486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2486" s="0" t="s">
-        <v>9284</v>
+        <v>9285</v>
       </c>
       <c r="B2486" s="0" t="s">
         <v>118</v>
       </c>
       <c r="D2486" s="0" t="s">
-        <v>9285</v>
+        <v>9286</v>
       </c>
       <c r="E2486" s="0" t="s">
-        <v>9286</v>
+        <v>9287</v>
       </c>
       <c r="F2486" s="0" t="s">
-        <v>9287</v>
+        <v>9288</v>
       </c>
     </row>
     <row r="2487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2487" s="0" t="s">
-        <v>9288</v>
+        <v>9289</v>
       </c>
       <c r="B2487" s="0" t="s">
         <v>118</v>
       </c>
       <c r="D2487" s="0" t="s">
-        <v>9289</v>
+        <v>9290</v>
       </c>
       <c r="E2487" s="0" t="s">
-        <v>9290</v>
+        <v>9291</v>
       </c>
       <c r="F2487" s="0" t="s">
-        <v>9291</v>
+        <v>9292</v>
       </c>
     </row>
     <row r="2488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2488" s="0" t="s">
-        <v>9292</v>
+        <v>9293</v>
       </c>
       <c r="B2488" s="0" t="s">
-        <v>291</v>
+        <v>118</v>
       </c>
       <c r="D2488" s="0" t="s">
-        <v>9293</v>
+        <v>9294</v>
       </c>
       <c r="E2488" s="0" t="s">
-        <v>9294</v>
+        <v>9295</v>
       </c>
       <c r="F2488" s="0" t="s">
-        <v>9295</v>
+        <v>9296</v>
       </c>
     </row>
     <row r="2489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2489" s="0" t="s">
-        <v>9296</v>
+        <v>9297</v>
       </c>
       <c r="B2489" s="0" t="s">
         <v>291</v>
       </c>
       <c r="D2489" s="0" t="s">
-        <v>9297</v>
+        <v>9298</v>
       </c>
       <c r="E2489" s="0" t="s">
-        <v>9298</v>
+        <v>9299</v>
       </c>
       <c r="F2489" s="0" t="s">
-        <v>9299</v>
-      </c>
-    </row>
-    <row r="2490" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>9300</v>
+      </c>
+    </row>
+    <row r="2490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2490" s="0" t="s">
-        <v>9300</v>
+        <v>9301</v>
       </c>
       <c r="B2490" s="0" t="s">
         <v>291</v>
       </c>
-      <c r="D2490" s="2" t="s">
-        <v>9301</v>
-      </c>
-      <c r="E2490" s="2" t="s">
+      <c r="D2490" s="0" t="s">
         <v>9302</v>
       </c>
-      <c r="F2490" s="2" t="s">
+      <c r="E2490" s="0" t="s">
         <v>9303</v>
       </c>
-    </row>
-    <row r="2491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2490" s="0" t="s">
+        <v>9304</v>
+      </c>
+    </row>
+    <row r="2491" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2491" s="0" t="s">
-        <v>9304</v>
+        <v>9305</v>
       </c>
       <c r="B2491" s="0" t="s">
         <v>291</v>
       </c>
-      <c r="D2491" s="0" t="s">
-        <v>9305</v>
-      </c>
-      <c r="E2491" s="0" t="s">
+      <c r="D2491" s="2" t="s">
         <v>9306</v>
       </c>
-      <c r="F2491" s="0" t="s">
+      <c r="E2491" s="2" t="s">
         <v>9307</v>
       </c>
-    </row>
-    <row r="2492" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2491" s="2" t="s">
+        <v>9308</v>
+      </c>
+    </row>
+    <row r="2492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2492" s="0" t="s">
-        <v>9308</v>
+        <v>9309</v>
       </c>
       <c r="B2492" s="0" t="s">
         <v>291</v>
       </c>
-      <c r="D2492" s="2" t="s">
-        <v>9309</v>
-      </c>
-      <c r="E2492" s="2" t="s">
+      <c r="D2492" s="0" t="s">
         <v>9310</v>
       </c>
-      <c r="F2492" s="2" t="s">
+      <c r="E2492" s="0" t="s">
         <v>9311</v>
       </c>
-    </row>
-    <row r="2493" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2492" s="0" t="s">
+        <v>9312</v>
+      </c>
+    </row>
+    <row r="2493" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2493" s="0" t="s">
-        <v>9312</v>
+        <v>9313</v>
       </c>
       <c r="B2493" s="0" t="s">
         <v>291</v>
       </c>
-      <c r="D2493" s="0" t="s">
-        <v>9313</v>
-      </c>
-      <c r="E2493" s="0" t="s">
+      <c r="D2493" s="2" t="s">
         <v>9314</v>
       </c>
-      <c r="F2493" s="0" t="s">
+      <c r="E2493" s="2" t="s">
         <v>9315</v>
+      </c>
+      <c r="F2493" s="2" t="s">
+        <v>9316</v>
       </c>
     </row>
     <row r="2494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2494" s="0" t="s">
-        <v>9316</v>
+        <v>9317</v>
       </c>
       <c r="B2494" s="0" t="s">
         <v>291</v>
       </c>
       <c r="D2494" s="0" t="s">
-        <v>9317</v>
+        <v>9318</v>
       </c>
       <c r="E2494" s="0" t="s">
-        <v>9318</v>
+        <v>9319</v>
       </c>
       <c r="F2494" s="0" t="s">
-        <v>9319</v>
+        <v>9320</v>
       </c>
     </row>
     <row r="2495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2495" s="0" t="s">
-        <v>9320</v>
+        <v>9321</v>
       </c>
       <c r="B2495" s="0" t="s">
         <v>291</v>
       </c>
       <c r="D2495" s="0" t="s">
-        <v>9321</v>
+        <v>9322</v>
       </c>
       <c r="E2495" s="0" t="s">
-        <v>9322</v>
+        <v>9323</v>
       </c>
       <c r="F2495" s="0" t="s">
-        <v>9323</v>
+        <v>9324</v>
       </c>
     </row>
     <row r="2496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2496" s="0" t="s">
-        <v>9324</v>
+        <v>9325</v>
       </c>
       <c r="B2496" s="0" t="s">
         <v>291</v>
       </c>
+      <c r="D2496" s="0" t="s">
+        <v>9326</v>
+      </c>
+      <c r="E2496" s="0" t="s">
+        <v>9327</v>
+      </c>
+      <c r="F2496" s="0" t="s">
+        <v>9328</v>
+      </c>
     </row>
     <row r="2497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2497" s="0" t="s">
-        <v>9325</v>
+        <v>9329</v>
       </c>
       <c r="B2497" s="0" t="s">
         <v>291</v>
       </c>
-      <c r="D2497" s="0" t="s">
-        <v>9326</v>
-      </c>
-      <c r="E2497" s="0" t="s">
-        <v>9327</v>
-      </c>
-      <c r="F2497" s="0" t="s">
-        <v>9328</v>
-      </c>
     </row>
     <row r="2498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2498" s="0" t="s">
-        <v>9329</v>
+        <v>9330</v>
       </c>
       <c r="B2498" s="0" t="s">
         <v>291</v>
       </c>
       <c r="D2498" s="0" t="s">
-        <v>9330</v>
+        <v>9331</v>
       </c>
       <c r="E2498" s="0" t="s">
-        <v>9331</v>
+        <v>9332</v>
       </c>
       <c r="F2498" s="0" t="s">
-        <v>9332</v>
+        <v>9333</v>
       </c>
     </row>
     <row r="2499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2499" s="0" t="s">
-        <v>9333</v>
+        <v>9334</v>
       </c>
       <c r="B2499" s="0" t="s">
-        <v>1592</v>
+        <v>291</v>
       </c>
       <c r="D2499" s="0" t="s">
-        <v>9334</v>
+        <v>9335</v>
       </c>
       <c r="E2499" s="0" t="s">
-        <v>9335</v>
+        <v>9336</v>
       </c>
       <c r="F2499" s="0" t="s">
-        <v>9336</v>
+        <v>9337</v>
       </c>
     </row>
     <row r="2500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2500" s="0" t="s">
-        <v>9337</v>
+        <v>9338</v>
       </c>
       <c r="B2500" s="0" t="s">
-        <v>291</v>
+        <v>1592</v>
       </c>
       <c r="D2500" s="0" t="s">
-        <v>9338</v>
+        <v>9339</v>
       </c>
       <c r="E2500" s="0" t="s">
-        <v>9339</v>
+        <v>9340</v>
       </c>
       <c r="F2500" s="0" t="s">
-        <v>9340</v>
+        <v>9341</v>
       </c>
     </row>
     <row r="2501" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2501" s="0" t="s">
-        <v>9341</v>
+        <v>9342</v>
       </c>
       <c r="B2501" s="0" t="s">
         <v>291</v>
       </c>
       <c r="D2501" s="0" t="s">
-        <v>9342</v>
+        <v>9343</v>
       </c>
       <c r="E2501" s="0" t="s">
-        <v>9343</v>
+        <v>9344</v>
       </c>
       <c r="F2501" s="0" t="s">
-        <v>9344</v>
+        <v>9345</v>
       </c>
     </row>
     <row r="2502" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2502" s="0" t="s">
-        <v>9345</v>
+        <v>9346</v>
       </c>
       <c r="B2502" s="0" t="s">
         <v>291</v>
       </c>
       <c r="D2502" s="0" t="s">
-        <v>9346</v>
+        <v>9347</v>
       </c>
       <c r="E2502" s="0" t="s">
-        <v>9347</v>
+        <v>9348</v>
       </c>
       <c r="F2502" s="0" t="s">
-        <v>9348</v>
+        <v>9349</v>
       </c>
     </row>
     <row r="2503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2503" s="0" t="s">
-        <v>9349</v>
+        <v>9350</v>
       </c>
       <c r="B2503" s="0" t="s">
-        <v>7170</v>
+        <v>291</v>
       </c>
       <c r="D2503" s="0" t="s">
-        <v>9350</v>
+        <v>9351</v>
       </c>
       <c r="E2503" s="0" t="s">
-        <v>9351</v>
+        <v>9352</v>
       </c>
       <c r="F2503" s="0" t="s">
-        <v>9352</v>
+        <v>9353</v>
       </c>
     </row>
     <row r="2504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2504" s="0" t="s">
-        <v>9353</v>
+        <v>9354</v>
       </c>
       <c r="B2504" s="0" t="s">
-        <v>291</v>
+        <v>7170</v>
       </c>
       <c r="D2504" s="0" t="s">
-        <v>9354</v>
+        <v>9355</v>
       </c>
       <c r="E2504" s="0" t="s">
-        <v>9355</v>
+        <v>9356</v>
       </c>
       <c r="F2504" s="0" t="s">
-        <v>9356</v>
+        <v>9357</v>
       </c>
     </row>
     <row r="2505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2505" s="0" t="s">
-        <v>9357</v>
+        <v>9358</v>
       </c>
       <c r="B2505" s="0" t="s">
         <v>291</v>
       </c>
       <c r="D2505" s="0" t="s">
-        <v>9358</v>
+        <v>9359</v>
       </c>
       <c r="E2505" s="0" t="s">
-        <v>9359</v>
+        <v>9360</v>
       </c>
       <c r="F2505" s="0" t="s">
-        <v>9360</v>
+        <v>9361</v>
       </c>
     </row>
     <row r="2506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2506" s="0" t="s">
-        <v>9361</v>
+        <v>9362</v>
       </c>
       <c r="B2506" s="0" t="s">
         <v>291</v>
       </c>
       <c r="D2506" s="0" t="s">
-        <v>9362</v>
+        <v>9363</v>
       </c>
       <c r="E2506" s="0" t="s">
-        <v>9363</v>
+        <v>9364</v>
       </c>
       <c r="F2506" s="0" t="s">
-        <v>9364</v>
+        <v>9365</v>
       </c>
     </row>
     <row r="2507" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2507" s="0" t="s">
-        <v>9365</v>
+        <v>9366</v>
       </c>
       <c r="B2507" s="0" t="s">
-        <v>9366</v>
+        <v>291</v>
       </c>
       <c r="D2507" s="0" t="s">
         <v>9367</v>
@@ -80308,194 +80322,194 @@
         <v>9375</v>
       </c>
       <c r="B2509" s="0" t="s">
-        <v>9371</v>
+        <v>9376</v>
       </c>
       <c r="D2509" s="0" t="s">
-        <v>9376</v>
+        <v>9377</v>
       </c>
       <c r="E2509" s="0" t="s">
-        <v>9377</v>
+        <v>9378</v>
       </c>
       <c r="F2509" s="0" t="s">
-        <v>9378</v>
+        <v>9379</v>
       </c>
     </row>
     <row r="2510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2510" s="0" t="s">
-        <v>9379</v>
+        <v>9380</v>
       </c>
       <c r="B2510" s="0" t="s">
-        <v>9371</v>
+        <v>9376</v>
       </c>
       <c r="D2510" s="0" t="s">
-        <v>4895</v>
+        <v>9381</v>
       </c>
       <c r="E2510" s="0" t="s">
-        <v>9380</v>
+        <v>9382</v>
       </c>
       <c r="F2510" s="0" t="s">
-        <v>9381</v>
+        <v>9383</v>
       </c>
     </row>
     <row r="2511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2511" s="0" t="s">
-        <v>9382</v>
+        <v>9384</v>
       </c>
       <c r="B2511" s="0" t="s">
-        <v>9371</v>
+        <v>9376</v>
       </c>
       <c r="D2511" s="0" t="s">
-        <v>9383</v>
+        <v>4895</v>
       </c>
       <c r="E2511" s="0" t="s">
-        <v>9384</v>
+        <v>9385</v>
       </c>
       <c r="F2511" s="0" t="s">
-        <v>9385</v>
+        <v>9386</v>
       </c>
     </row>
     <row r="2512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2512" s="0" t="s">
-        <v>9386</v>
+        <v>9387</v>
       </c>
       <c r="B2512" s="0" t="s">
-        <v>9371</v>
+        <v>9376</v>
       </c>
       <c r="D2512" s="0" t="s">
-        <v>9387</v>
+        <v>9388</v>
       </c>
       <c r="E2512" s="0" t="s">
-        <v>9388</v>
+        <v>9389</v>
       </c>
       <c r="F2512" s="0" t="s">
-        <v>9389</v>
+        <v>9390</v>
       </c>
     </row>
     <row r="2513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2513" s="0" t="s">
-        <v>9390</v>
+        <v>9391</v>
       </c>
       <c r="B2513" s="0" t="s">
-        <v>9371</v>
+        <v>9376</v>
       </c>
       <c r="D2513" s="0" t="s">
-        <v>9391</v>
+        <v>9392</v>
       </c>
       <c r="E2513" s="0" t="s">
-        <v>1553</v>
+        <v>9393</v>
       </c>
       <c r="F2513" s="0" t="s">
-        <v>9392</v>
+        <v>9394</v>
       </c>
     </row>
     <row r="2514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2514" s="0" t="s">
-        <v>9393</v>
+        <v>9395</v>
       </c>
       <c r="B2514" s="0" t="s">
-        <v>9371</v>
+        <v>9376</v>
       </c>
       <c r="D2514" s="0" t="s">
-        <v>9394</v>
+        <v>9396</v>
       </c>
       <c r="E2514" s="0" t="s">
-        <v>9395</v>
+        <v>1553</v>
       </c>
       <c r="F2514" s="0" t="s">
-        <v>9396</v>
+        <v>9397</v>
       </c>
     </row>
     <row r="2515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2515" s="0" t="s">
-        <v>9397</v>
+        <v>9398</v>
       </c>
       <c r="B2515" s="0" t="s">
-        <v>9371</v>
+        <v>9376</v>
       </c>
       <c r="D2515" s="0" t="s">
-        <v>9398</v>
+        <v>9399</v>
       </c>
       <c r="E2515" s="0" t="s">
-        <v>9399</v>
+        <v>9400</v>
       </c>
       <c r="F2515" s="0" t="s">
-        <v>9400</v>
+        <v>9401</v>
       </c>
     </row>
     <row r="2516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2516" s="0" t="s">
-        <v>9401</v>
+        <v>9402</v>
       </c>
       <c r="B2516" s="0" t="s">
-        <v>9371</v>
+        <v>9376</v>
       </c>
       <c r="D2516" s="0" t="s">
-        <v>9402</v>
+        <v>9403</v>
       </c>
       <c r="E2516" s="0" t="s">
-        <v>9403</v>
+        <v>9404</v>
       </c>
       <c r="F2516" s="0" t="s">
-        <v>9404</v>
+        <v>9405</v>
       </c>
     </row>
     <row r="2517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2517" s="0" t="s">
-        <v>9405</v>
+        <v>9406</v>
       </c>
       <c r="B2517" s="0" t="s">
-        <v>9371</v>
+        <v>9376</v>
       </c>
       <c r="D2517" s="0" t="s">
-        <v>9406</v>
+        <v>9407</v>
       </c>
       <c r="E2517" s="0" t="s">
-        <v>9407</v>
+        <v>9408</v>
       </c>
       <c r="F2517" s="0" t="s">
-        <v>9408</v>
+        <v>9409</v>
       </c>
     </row>
     <row r="2518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2518" s="0" t="s">
-        <v>9409</v>
+        <v>9410</v>
       </c>
       <c r="B2518" s="0" t="s">
-        <v>4255</v>
+        <v>9376</v>
       </c>
       <c r="D2518" s="0" t="s">
-        <v>9410</v>
+        <v>9411</v>
       </c>
       <c r="E2518" s="0" t="s">
-        <v>9411</v>
+        <v>9412</v>
       </c>
       <c r="F2518" s="0" t="s">
-        <v>9412</v>
+        <v>9413</v>
       </c>
     </row>
     <row r="2519" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2519" s="0" t="s">
-        <v>9413</v>
+        <v>9414</v>
       </c>
       <c r="B2519" s="0" t="s">
         <v>4255</v>
       </c>
       <c r="D2519" s="0" t="s">
-        <v>9414</v>
+        <v>9415</v>
       </c>
       <c r="E2519" s="0" t="s">
-        <v>9415</v>
+        <v>9416</v>
       </c>
       <c r="F2519" s="0" t="s">
-        <v>9416</v>
+        <v>9417</v>
       </c>
     </row>
     <row r="2520" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2520" s="0" t="s">
-        <v>9417</v>
+        <v>9418</v>
       </c>
       <c r="B2520" s="0" t="s">
-        <v>9418</v>
+        <v>4255</v>
       </c>
       <c r="D2520" s="0" t="s">
         <v>9419</v>
@@ -80512,143 +80526,143 @@
         <v>9422</v>
       </c>
       <c r="B2521" s="0" t="s">
-        <v>53</v>
+        <v>9423</v>
       </c>
       <c r="D2521" s="0" t="s">
-        <v>9423</v>
+        <v>9424</v>
       </c>
       <c r="E2521" s="0" t="s">
-        <v>9424</v>
+        <v>9425</v>
       </c>
       <c r="F2521" s="0" t="s">
-        <v>9425</v>
+        <v>9426</v>
       </c>
     </row>
     <row r="2522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2522" s="0" t="s">
-        <v>9426</v>
+        <v>9427</v>
       </c>
       <c r="B2522" s="0" t="s">
-        <v>2244</v>
+        <v>53</v>
       </c>
       <c r="D2522" s="0" t="s">
-        <v>9427</v>
+        <v>9428</v>
       </c>
       <c r="E2522" s="0" t="s">
-        <v>9428</v>
+        <v>9429</v>
       </c>
       <c r="F2522" s="0" t="s">
-        <v>9429</v>
+        <v>9430</v>
       </c>
     </row>
     <row r="2523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2523" s="0" t="s">
-        <v>9430</v>
+        <v>9431</v>
       </c>
       <c r="B2523" s="0" t="s">
         <v>2244</v>
       </c>
       <c r="D2523" s="0" t="s">
-        <v>9431</v>
+        <v>9432</v>
       </c>
       <c r="E2523" s="0" t="s">
-        <v>9432</v>
+        <v>9433</v>
       </c>
       <c r="F2523" s="0" t="s">
-        <v>9433</v>
+        <v>9434</v>
       </c>
     </row>
     <row r="2524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2524" s="0" t="s">
-        <v>9434</v>
+        <v>9435</v>
       </c>
       <c r="B2524" s="0" t="s">
-        <v>378</v>
+        <v>2244</v>
       </c>
       <c r="D2524" s="0" t="s">
-        <v>9435</v>
+        <v>9436</v>
       </c>
       <c r="E2524" s="0" t="s">
-        <v>9436</v>
+        <v>9437</v>
       </c>
       <c r="F2524" s="0" t="s">
-        <v>9437</v>
+        <v>9438</v>
       </c>
     </row>
     <row r="2525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2525" s="0" t="s">
-        <v>9438</v>
+        <v>9439</v>
       </c>
       <c r="B2525" s="0" t="s">
         <v>378</v>
       </c>
       <c r="D2525" s="0" t="s">
-        <v>9439</v>
+        <v>9440</v>
       </c>
       <c r="E2525" s="0" t="s">
-        <v>9440</v>
+        <v>9441</v>
       </c>
       <c r="F2525" s="0" t="s">
-        <v>9441</v>
+        <v>9442</v>
       </c>
     </row>
     <row r="2526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2526" s="0" t="s">
-        <v>9442</v>
+        <v>9443</v>
       </c>
       <c r="B2526" s="0" t="s">
         <v>378</v>
       </c>
       <c r="D2526" s="0" t="s">
-        <v>9443</v>
+        <v>9444</v>
       </c>
       <c r="E2526" s="0" t="s">
-        <v>9444</v>
+        <v>9445</v>
       </c>
       <c r="F2526" s="0" t="s">
-        <v>9445</v>
+        <v>9446</v>
       </c>
     </row>
     <row r="2527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2527" s="0" t="s">
-        <v>9446</v>
+        <v>9447</v>
       </c>
       <c r="B2527" s="0" t="s">
-        <v>2719</v>
+        <v>378</v>
       </c>
       <c r="D2527" s="0" t="s">
-        <v>9447</v>
+        <v>9448</v>
       </c>
       <c r="E2527" s="0" t="s">
-        <v>9448</v>
+        <v>9449</v>
       </c>
       <c r="F2527" s="0" t="s">
-        <v>9449</v>
+        <v>9450</v>
       </c>
     </row>
     <row r="2528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2528" s="0" t="s">
-        <v>9450</v>
+        <v>9451</v>
       </c>
       <c r="B2528" s="0" t="s">
-        <v>624</v>
+        <v>2719</v>
       </c>
       <c r="D2528" s="0" t="s">
-        <v>9451</v>
+        <v>9452</v>
       </c>
       <c r="E2528" s="0" t="s">
-        <v>9452</v>
+        <v>9453</v>
       </c>
       <c r="F2528" s="0" t="s">
-        <v>9453</v>
+        <v>9454</v>
       </c>
     </row>
     <row r="2529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2529" s="0" t="s">
-        <v>9454</v>
+        <v>9455</v>
       </c>
       <c r="B2529" s="0" t="s">
-        <v>9455</v>
+        <v>624</v>
       </c>
       <c r="D2529" s="0" t="s">
         <v>9456</v>
@@ -80665,24 +80679,24 @@
         <v>9459</v>
       </c>
       <c r="B2530" s="0" t="s">
-        <v>53</v>
+        <v>9460</v>
       </c>
       <c r="D2530" s="0" t="s">
-        <v>9460</v>
+        <v>9461</v>
       </c>
       <c r="E2530" s="0" t="s">
-        <v>9461</v>
+        <v>9462</v>
       </c>
       <c r="F2530" s="0" t="s">
-        <v>9462</v>
+        <v>9463</v>
       </c>
     </row>
     <row r="2531" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2531" s="0" t="s">
-        <v>9463</v>
+        <v>9464</v>
       </c>
       <c r="B2531" s="0" t="s">
-        <v>9464</v>
+        <v>53</v>
       </c>
       <c r="D2531" s="0" t="s">
         <v>9465</v>
@@ -80699,92 +80713,89 @@
         <v>9468</v>
       </c>
       <c r="B2532" s="0" t="s">
-        <v>7170</v>
+        <v>9469</v>
       </c>
       <c r="D2532" s="0" t="s">
-        <v>9469</v>
+        <v>9470</v>
       </c>
       <c r="E2532" s="0" t="s">
-        <v>9470</v>
+        <v>9471</v>
       </c>
       <c r="F2532" s="0" t="s">
-        <v>9471</v>
-      </c>
-    </row>
-    <row r="2533" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>9472</v>
+      </c>
+    </row>
+    <row r="2533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2533" s="0" t="s">
-        <v>9472</v>
+        <v>9473</v>
       </c>
       <c r="B2533" s="0" t="s">
         <v>7170</v>
       </c>
-      <c r="D2533" s="2" t="s">
-        <v>9473</v>
-      </c>
-      <c r="E2533" s="2" t="s">
+      <c r="D2533" s="0" t="s">
         <v>9474</v>
       </c>
-      <c r="F2533" s="2" t="s">
+      <c r="E2533" s="0" t="s">
         <v>9475</v>
       </c>
-    </row>
-    <row r="2534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2533" s="0" t="s">
+        <v>9476</v>
+      </c>
+    </row>
+    <row r="2534" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2534" s="0" t="s">
-        <v>9476</v>
+        <v>9477</v>
       </c>
       <c r="B2534" s="0" t="s">
-        <v>1334</v>
-      </c>
-      <c r="D2534" s="0" t="s">
-        <v>9477</v>
-      </c>
-      <c r="E2534" s="0" t="s">
+        <v>7170</v>
+      </c>
+      <c r="D2534" s="2" t="s">
         <v>9478</v>
       </c>
-      <c r="F2534" s="0" t="s">
+      <c r="E2534" s="2" t="s">
         <v>9479</v>
+      </c>
+      <c r="F2534" s="2" t="s">
+        <v>9480</v>
       </c>
     </row>
     <row r="2535" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2535" s="0" t="s">
-        <v>9480</v>
+        <v>9481</v>
       </c>
       <c r="B2535" s="0" t="s">
-        <v>53</v>
+        <v>1334</v>
       </c>
       <c r="D2535" s="0" t="s">
-        <v>9481</v>
+        <v>9482</v>
       </c>
       <c r="E2535" s="0" t="s">
-        <v>9482</v>
+        <v>9483</v>
       </c>
       <c r="F2535" s="0" t="s">
-        <v>9483</v>
+        <v>9484</v>
       </c>
     </row>
     <row r="2536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2536" s="0" t="s">
-        <v>9484</v>
+        <v>9485</v>
       </c>
       <c r="B2536" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="C2536" s="0" t="s">
-        <v>990</v>
-      </c>
       <c r="D2536" s="0" t="s">
-        <v>9485</v>
+        <v>9486</v>
       </c>
       <c r="E2536" s="0" t="s">
-        <v>9486</v>
+        <v>9487</v>
       </c>
       <c r="F2536" s="0" t="s">
-        <v>9487</v>
+        <v>9488</v>
       </c>
     </row>
     <row r="2537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2537" s="0" t="s">
-        <v>9488</v>
+        <v>9489</v>
       </c>
       <c r="B2537" s="0" t="s">
         <v>53</v>
@@ -80793,18 +80804,18 @@
         <v>990</v>
       </c>
       <c r="D2537" s="0" t="s">
-        <v>8270</v>
+        <v>9490</v>
       </c>
       <c r="E2537" s="0" t="s">
-        <v>8271</v>
+        <v>9491</v>
       </c>
       <c r="F2537" s="0" t="s">
-        <v>8272</v>
+        <v>9492</v>
       </c>
     </row>
     <row r="2538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2538" s="0" t="s">
-        <v>9489</v>
+        <v>9493</v>
       </c>
       <c r="B2538" s="0" t="s">
         <v>53</v>
@@ -80813,18 +80824,18 @@
         <v>990</v>
       </c>
       <c r="D2538" s="0" t="s">
-        <v>3310</v>
+        <v>8270</v>
       </c>
       <c r="E2538" s="0" t="s">
-        <v>1329</v>
+        <v>8271</v>
       </c>
       <c r="F2538" s="0" t="s">
-        <v>1330</v>
+        <v>8272</v>
       </c>
     </row>
     <row r="2539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2539" s="0" t="s">
-        <v>9490</v>
+        <v>9494</v>
       </c>
       <c r="B2539" s="0" t="s">
         <v>53</v>
@@ -80833,33 +80844,33 @@
         <v>990</v>
       </c>
       <c r="D2539" s="0" t="s">
-        <v>9491</v>
+        <v>3310</v>
       </c>
       <c r="E2539" s="0" t="s">
-        <v>9492</v>
+        <v>1329</v>
       </c>
       <c r="F2539" s="0" t="s">
-        <v>9453</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="2540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2540" s="0" t="s">
-        <v>9493</v>
+        <v>9495</v>
       </c>
       <c r="B2540" s="0" t="s">
-        <v>1847</v>
+        <v>53</v>
       </c>
       <c r="C2540" s="0" t="s">
-        <v>9494</v>
+        <v>990</v>
       </c>
       <c r="D2540" s="0" t="s">
-        <v>9495</v>
+        <v>9496</v>
       </c>
       <c r="E2540" s="0" t="s">
-        <v>9496</v>
+        <v>9497</v>
       </c>
       <c r="F2540" s="0" t="s">
-        <v>9497</v>
+        <v>9458</v>
       </c>
     </row>
     <row r="2541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -80870,178 +80881,181 @@
         <v>1847</v>
       </c>
       <c r="C2541" s="0" t="s">
-        <v>9494</v>
+        <v>9499</v>
       </c>
       <c r="D2541" s="0" t="s">
-        <v>9499</v>
+        <v>9500</v>
       </c>
       <c r="E2541" s="0" t="s">
-        <v>9500</v>
+        <v>9501</v>
       </c>
       <c r="F2541" s="0" t="s">
-        <v>9501</v>
+        <v>9502</v>
       </c>
     </row>
     <row r="2542" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2542" s="0" t="s">
-        <v>9502</v>
+        <v>9503</v>
       </c>
       <c r="B2542" s="0" t="s">
         <v>1847</v>
       </c>
       <c r="C2542" s="0" t="s">
-        <v>9494</v>
+        <v>9499</v>
       </c>
       <c r="D2542" s="0" t="s">
-        <v>9503</v>
+        <v>9504</v>
       </c>
       <c r="E2542" s="0" t="s">
-        <v>9504</v>
+        <v>9505</v>
       </c>
       <c r="F2542" s="0" t="s">
-        <v>9505</v>
+        <v>9506</v>
       </c>
     </row>
     <row r="2543" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2543" s="0" t="s">
-        <v>9506</v>
+        <v>9507</v>
       </c>
       <c r="B2543" s="0" t="s">
         <v>1847</v>
       </c>
       <c r="C2543" s="0" t="s">
-        <v>9494</v>
+        <v>9499</v>
       </c>
       <c r="D2543" s="0" t="s">
-        <v>9507</v>
+        <v>9508</v>
       </c>
       <c r="E2543" s="0" t="s">
-        <v>5709</v>
+        <v>9509</v>
       </c>
       <c r="F2543" s="0" t="s">
-        <v>9508</v>
+        <v>9510</v>
       </c>
     </row>
     <row r="2544" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2544" s="0" t="s">
-        <v>9509</v>
+        <v>9511</v>
       </c>
       <c r="B2544" s="0" t="s">
         <v>1847</v>
       </c>
       <c r="C2544" s="0" t="s">
-        <v>9494</v>
+        <v>9499</v>
       </c>
       <c r="D2544" s="0" t="s">
-        <v>9510</v>
+        <v>9512</v>
       </c>
       <c r="E2544" s="0" t="s">
-        <v>9511</v>
+        <v>5709</v>
       </c>
       <c r="F2544" s="0" t="s">
-        <v>9512</v>
+        <v>9513</v>
       </c>
     </row>
     <row r="2545" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2545" s="0" t="s">
-        <v>9513</v>
+        <v>9514</v>
       </c>
       <c r="B2545" s="0" t="s">
         <v>1847</v>
       </c>
       <c r="C2545" s="0" t="s">
-        <v>9494</v>
+        <v>9499</v>
       </c>
       <c r="D2545" s="0" t="s">
-        <v>9514</v>
+        <v>9515</v>
       </c>
       <c r="E2545" s="0" t="s">
-        <v>9515</v>
+        <v>9516</v>
       </c>
       <c r="F2545" s="0" t="s">
-        <v>9516</v>
+        <v>9517</v>
       </c>
     </row>
     <row r="2546" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2546" s="0" t="s">
-        <v>9517</v>
+        <v>9518</v>
       </c>
       <c r="B2546" s="0" t="s">
         <v>1847</v>
       </c>
       <c r="C2546" s="0" t="s">
-        <v>9494</v>
+        <v>9499</v>
       </c>
       <c r="D2546" s="0" t="s">
-        <v>9518</v>
+        <v>9519</v>
       </c>
       <c r="E2546" s="0" t="s">
-        <v>9519</v>
+        <v>9520</v>
       </c>
       <c r="F2546" s="0" t="s">
-        <v>9520</v>
+        <v>9521</v>
       </c>
     </row>
     <row r="2547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2547" s="0" t="s">
-        <v>9521</v>
+        <v>9522</v>
       </c>
       <c r="B2547" s="0" t="s">
         <v>1847</v>
       </c>
       <c r="C2547" s="0" t="s">
-        <v>9494</v>
+        <v>9499</v>
       </c>
       <c r="D2547" s="0" t="s">
-        <v>9522</v>
+        <v>9523</v>
       </c>
       <c r="E2547" s="0" t="s">
-        <v>9522</v>
+        <v>9524</v>
       </c>
       <c r="F2547" s="0" t="s">
-        <v>9522</v>
+        <v>9525</v>
       </c>
     </row>
     <row r="2548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2548" s="0" t="s">
-        <v>9523</v>
+        <v>9526</v>
       </c>
       <c r="B2548" s="0" t="s">
-        <v>1342</v>
+        <v>1847</v>
+      </c>
+      <c r="C2548" s="0" t="s">
+        <v>9499</v>
       </c>
       <c r="D2548" s="0" t="s">
-        <v>1490</v>
+        <v>9527</v>
       </c>
       <c r="E2548" s="0" t="s">
-        <v>9524</v>
+        <v>9527</v>
       </c>
       <c r="F2548" s="0" t="s">
-        <v>9525</v>
+        <v>9527</v>
       </c>
     </row>
     <row r="2549" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2549" s="0" t="s">
-        <v>9526</v>
+        <v>9528</v>
       </c>
       <c r="B2549" s="0" t="s">
-        <v>4716</v>
+        <v>1342</v>
       </c>
       <c r="D2549" s="0" t="s">
-        <v>9527</v>
+        <v>1490</v>
       </c>
       <c r="E2549" s="0" t="s">
-        <v>9528</v>
+        <v>9529</v>
       </c>
       <c r="F2549" s="0" t="s">
-        <v>9529</v>
+        <v>9530</v>
       </c>
     </row>
     <row r="2550" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2550" s="0" t="s">
-        <v>9530</v>
+        <v>9531</v>
       </c>
       <c r="B2550" s="0" t="s">
-        <v>9531</v>
+        <v>4716</v>
       </c>
       <c r="D2550" s="0" t="s">
         <v>9532</v>
@@ -81058,500 +81072,500 @@
         <v>9535</v>
       </c>
       <c r="B2551" s="0" t="s">
-        <v>4716</v>
+        <v>9536</v>
       </c>
       <c r="D2551" s="0" t="s">
-        <v>9536</v>
+        <v>9537</v>
       </c>
       <c r="E2551" s="0" t="s">
-        <v>9537</v>
+        <v>9538</v>
       </c>
       <c r="F2551" s="0" t="s">
-        <v>9538</v>
+        <v>9539</v>
       </c>
     </row>
     <row r="2552" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2552" s="0" t="s">
-        <v>9539</v>
+        <v>9540</v>
       </c>
       <c r="B2552" s="0" t="s">
         <v>4716</v>
       </c>
       <c r="D2552" s="0" t="s">
-        <v>9540</v>
+        <v>9541</v>
       </c>
       <c r="E2552" s="0" t="s">
-        <v>9541</v>
+        <v>9542</v>
       </c>
       <c r="F2552" s="0" t="s">
-        <v>9542</v>
+        <v>9543</v>
       </c>
     </row>
     <row r="2553" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2553" s="0" t="s">
-        <v>9543</v>
+        <v>9544</v>
       </c>
       <c r="B2553" s="0" t="s">
-        <v>2960</v>
+        <v>4716</v>
       </c>
       <c r="D2553" s="0" t="s">
-        <v>9544</v>
+        <v>9545</v>
       </c>
       <c r="E2553" s="0" t="s">
-        <v>9545</v>
+        <v>9546</v>
       </c>
       <c r="F2553" s="0" t="s">
-        <v>9546</v>
+        <v>9547</v>
       </c>
     </row>
     <row r="2554" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2554" s="0" t="s">
-        <v>9547</v>
+        <v>9548</v>
       </c>
       <c r="B2554" s="0" t="s">
         <v>2960</v>
       </c>
       <c r="D2554" s="0" t="s">
-        <v>9548</v>
+        <v>9549</v>
       </c>
       <c r="E2554" s="0" t="s">
-        <v>9549</v>
+        <v>9550</v>
       </c>
       <c r="F2554" s="0" t="s">
-        <v>9550</v>
+        <v>9551</v>
       </c>
     </row>
     <row r="2555" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2555" s="0" t="s">
-        <v>9551</v>
+        <v>9552</v>
       </c>
       <c r="B2555" s="0" t="s">
         <v>2960</v>
       </c>
       <c r="D2555" s="0" t="s">
-        <v>9552</v>
+        <v>9553</v>
       </c>
       <c r="E2555" s="0" t="s">
-        <v>9553</v>
+        <v>9554</v>
       </c>
       <c r="F2555" s="0" t="s">
-        <v>9554</v>
-      </c>
-    </row>
-    <row r="2556" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>9555</v>
+      </c>
+    </row>
+    <row r="2556" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2556" s="0" t="s">
-        <v>9555</v>
+        <v>9556</v>
       </c>
       <c r="B2556" s="0" t="s">
         <v>2960</v>
       </c>
       <c r="D2556" s="0" t="s">
-        <v>9556</v>
-      </c>
-      <c r="E2556" s="2" t="s">
         <v>9557</v>
       </c>
+      <c r="E2556" s="0" t="s">
+        <v>9558</v>
+      </c>
       <c r="F2556" s="0" t="s">
-        <v>9558</v>
-      </c>
-    </row>
-    <row r="2557" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>9559</v>
+      </c>
+    </row>
+    <row r="2557" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2557" s="0" t="s">
-        <v>9559</v>
+        <v>9560</v>
       </c>
       <c r="B2557" s="0" t="s">
         <v>2960</v>
       </c>
       <c r="D2557" s="0" t="s">
-        <v>9560</v>
-      </c>
-      <c r="E2557" s="0" t="s">
         <v>9561</v>
       </c>
+      <c r="E2557" s="2" t="s">
+        <v>9562</v>
+      </c>
       <c r="F2557" s="0" t="s">
-        <v>9562</v>
+        <v>9563</v>
       </c>
     </row>
     <row r="2558" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2558" s="0" t="s">
-        <v>9563</v>
+        <v>9564</v>
       </c>
       <c r="B2558" s="0" t="s">
         <v>2960</v>
       </c>
       <c r="D2558" s="0" t="s">
-        <v>9564</v>
+        <v>9565</v>
       </c>
       <c r="E2558" s="0" t="s">
-        <v>9565</v>
+        <v>9566</v>
       </c>
       <c r="F2558" s="0" t="s">
-        <v>9566</v>
+        <v>9567</v>
       </c>
     </row>
     <row r="2559" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2559" s="0" t="s">
-        <v>9567</v>
+        <v>9568</v>
       </c>
       <c r="B2559" s="0" t="s">
-        <v>77</v>
+        <v>2960</v>
       </c>
       <c r="D2559" s="0" t="s">
-        <v>9568</v>
+        <v>9569</v>
       </c>
       <c r="E2559" s="0" t="s">
-        <v>9569</v>
+        <v>9570</v>
       </c>
       <c r="F2559" s="0" t="s">
-        <v>9570</v>
+        <v>9571</v>
       </c>
     </row>
     <row r="2560" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2560" s="0" t="s">
-        <v>9571</v>
+        <v>9572</v>
       </c>
       <c r="B2560" s="0" t="s">
-        <v>1219</v>
+        <v>77</v>
       </c>
       <c r="D2560" s="0" t="s">
-        <v>9572</v>
+        <v>9573</v>
       </c>
       <c r="E2560" s="0" t="s">
-        <v>9573</v>
+        <v>9574</v>
       </c>
       <c r="F2560" s="0" t="s">
-        <v>9574</v>
+        <v>9575</v>
       </c>
     </row>
     <row r="2561" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2561" s="0" t="s">
-        <v>9575</v>
+        <v>9576</v>
       </c>
       <c r="B2561" s="0" t="s">
         <v>1219</v>
       </c>
       <c r="D2561" s="0" t="s">
-        <v>9576</v>
+        <v>9577</v>
       </c>
       <c r="E2561" s="0" t="s">
-        <v>9577</v>
+        <v>9578</v>
       </c>
       <c r="F2561" s="0" t="s">
-        <v>9578</v>
+        <v>9579</v>
       </c>
     </row>
     <row r="2562" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2562" s="0" t="s">
-        <v>9579</v>
+        <v>9580</v>
       </c>
       <c r="B2562" s="0" t="s">
         <v>1219</v>
       </c>
       <c r="D2562" s="0" t="s">
-        <v>9580</v>
+        <v>9581</v>
       </c>
       <c r="E2562" s="0" t="s">
-        <v>9581</v>
+        <v>9582</v>
       </c>
       <c r="F2562" s="0" t="s">
-        <v>9582</v>
+        <v>9583</v>
       </c>
     </row>
     <row r="2563" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2563" s="0" t="s">
-        <v>9583</v>
+        <v>9584</v>
       </c>
       <c r="B2563" s="0" t="s">
-        <v>1339</v>
+        <v>1219</v>
       </c>
       <c r="D2563" s="0" t="s">
-        <v>9584</v>
+        <v>9585</v>
       </c>
       <c r="E2563" s="0" t="s">
-        <v>9585</v>
+        <v>9586</v>
       </c>
       <c r="F2563" s="0" t="s">
-        <v>9586</v>
+        <v>9587</v>
       </c>
     </row>
     <row r="2564" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2564" s="0" t="s">
-        <v>9587</v>
+        <v>9588</v>
       </c>
       <c r="B2564" s="0" t="s">
-        <v>1432</v>
+        <v>1339</v>
       </c>
       <c r="D2564" s="0" t="s">
-        <v>9588</v>
+        <v>9589</v>
       </c>
       <c r="E2564" s="0" t="s">
-        <v>9589</v>
+        <v>9590</v>
       </c>
       <c r="F2564" s="0" t="s">
-        <v>9590</v>
+        <v>9591</v>
       </c>
     </row>
     <row r="2565" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2565" s="0" t="s">
-        <v>9591</v>
+        <v>9592</v>
       </c>
       <c r="B2565" s="0" t="s">
-        <v>1334</v>
+        <v>1432</v>
       </c>
       <c r="D2565" s="0" t="s">
-        <v>9592</v>
+        <v>9593</v>
       </c>
       <c r="E2565" s="0" t="s">
-        <v>9593</v>
+        <v>9594</v>
       </c>
       <c r="F2565" s="0" t="s">
-        <v>9594</v>
+        <v>9595</v>
       </c>
     </row>
     <row r="2566" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2566" s="0" t="s">
-        <v>9595</v>
+        <v>9596</v>
       </c>
       <c r="B2566" s="0" t="s">
-        <v>373</v>
+        <v>1334</v>
       </c>
       <c r="D2566" s="0" t="s">
-        <v>9596</v>
+        <v>9597</v>
       </c>
       <c r="E2566" s="0" t="s">
-        <v>9597</v>
+        <v>9598</v>
       </c>
       <c r="F2566" s="0" t="s">
-        <v>9598</v>
+        <v>9599</v>
       </c>
     </row>
     <row r="2567" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2567" s="0" t="s">
-        <v>9599</v>
+        <v>9600</v>
       </c>
       <c r="B2567" s="0" t="s">
         <v>373</v>
       </c>
       <c r="D2567" s="0" t="s">
-        <v>9600</v>
+        <v>9601</v>
       </c>
       <c r="E2567" s="0" t="s">
-        <v>9601</v>
+        <v>9602</v>
       </c>
       <c r="F2567" s="0" t="s">
-        <v>9602</v>
+        <v>9603</v>
       </c>
     </row>
     <row r="2568" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2568" s="0" t="s">
-        <v>9603</v>
+        <v>9604</v>
       </c>
       <c r="B2568" s="0" t="s">
         <v>373</v>
       </c>
       <c r="D2568" s="0" t="s">
-        <v>9604</v>
+        <v>9605</v>
       </c>
       <c r="E2568" s="0" t="s">
-        <v>9605</v>
+        <v>9606</v>
       </c>
       <c r="F2568" s="0" t="s">
-        <v>9606</v>
+        <v>9607</v>
       </c>
     </row>
     <row r="2569" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2569" s="0" t="s">
-        <v>9607</v>
+        <v>9608</v>
       </c>
       <c r="B2569" s="0" t="s">
         <v>373</v>
       </c>
       <c r="D2569" s="0" t="s">
-        <v>9608</v>
+        <v>9609</v>
       </c>
       <c r="E2569" s="0" t="s">
-        <v>9609</v>
+        <v>9610</v>
       </c>
       <c r="F2569" s="0" t="s">
-        <v>9610</v>
+        <v>9611</v>
       </c>
     </row>
     <row r="2570" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2570" s="0" t="s">
-        <v>9611</v>
+        <v>9612</v>
       </c>
       <c r="B2570" s="0" t="s">
         <v>373</v>
       </c>
       <c r="D2570" s="0" t="s">
-        <v>9612</v>
+        <v>9613</v>
       </c>
       <c r="E2570" s="0" t="s">
-        <v>2524</v>
+        <v>9614</v>
       </c>
       <c r="F2570" s="0" t="s">
-        <v>9613</v>
+        <v>9615</v>
       </c>
     </row>
     <row r="2571" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2571" s="0" t="s">
-        <v>9614</v>
+        <v>9616</v>
       </c>
       <c r="B2571" s="0" t="s">
-        <v>1417</v>
+        <v>373</v>
       </c>
       <c r="D2571" s="0" t="s">
-        <v>9615</v>
+        <v>9617</v>
       </c>
       <c r="E2571" s="0" t="s">
-        <v>9616</v>
+        <v>2524</v>
       </c>
       <c r="F2571" s="0" t="s">
-        <v>9617</v>
+        <v>9618</v>
       </c>
     </row>
     <row r="2572" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2572" s="0" t="s">
-        <v>9618</v>
+        <v>9619</v>
       </c>
       <c r="B2572" s="0" t="s">
         <v>1417</v>
       </c>
       <c r="D2572" s="0" t="s">
-        <v>9619</v>
+        <v>9620</v>
       </c>
       <c r="E2572" s="0" t="s">
-        <v>9620</v>
+        <v>9621</v>
       </c>
       <c r="F2572" s="0" t="s">
-        <v>9621</v>
+        <v>9622</v>
       </c>
     </row>
     <row r="2573" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2573" s="0" t="s">
-        <v>9622</v>
+        <v>9623</v>
       </c>
       <c r="B2573" s="0" t="s">
         <v>1417</v>
       </c>
       <c r="D2573" s="0" t="s">
-        <v>9623</v>
+        <v>9624</v>
       </c>
       <c r="E2573" s="0" t="s">
-        <v>9624</v>
+        <v>9625</v>
       </c>
       <c r="F2573" s="0" t="s">
-        <v>9625</v>
+        <v>9626</v>
       </c>
     </row>
     <row r="2574" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2574" s="0" t="s">
-        <v>9626</v>
+        <v>9627</v>
       </c>
       <c r="B2574" s="0" t="s">
         <v>1417</v>
       </c>
       <c r="D2574" s="0" t="s">
-        <v>9627</v>
+        <v>9628</v>
       </c>
       <c r="E2574" s="0" t="s">
-        <v>9628</v>
+        <v>9629</v>
       </c>
       <c r="F2574" s="0" t="s">
-        <v>9629</v>
+        <v>9630</v>
       </c>
     </row>
     <row r="2575" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2575" s="0" t="s">
-        <v>9630</v>
+        <v>9631</v>
       </c>
       <c r="B2575" s="0" t="s">
         <v>1417</v>
       </c>
       <c r="D2575" s="0" t="s">
-        <v>9631</v>
+        <v>9632</v>
       </c>
       <c r="E2575" s="0" t="s">
-        <v>9632</v>
+        <v>9633</v>
       </c>
       <c r="F2575" s="0" t="s">
-        <v>9633</v>
+        <v>9634</v>
       </c>
     </row>
     <row r="2576" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2576" s="0" t="s">
-        <v>9634</v>
+        <v>9635</v>
       </c>
       <c r="B2576" s="0" t="s">
         <v>1417</v>
       </c>
       <c r="D2576" s="0" t="s">
-        <v>9635</v>
+        <v>9636</v>
       </c>
       <c r="E2576" s="0" t="s">
-        <v>9636</v>
+        <v>9637</v>
       </c>
       <c r="F2576" s="0" t="s">
-        <v>9637</v>
+        <v>9638</v>
       </c>
     </row>
     <row r="2577" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2577" s="0" t="s">
-        <v>9638</v>
+        <v>9639</v>
       </c>
       <c r="B2577" s="0" t="s">
         <v>1417</v>
       </c>
       <c r="D2577" s="0" t="s">
-        <v>9639</v>
+        <v>9640</v>
       </c>
       <c r="E2577" s="0" t="s">
-        <v>9640</v>
+        <v>9641</v>
       </c>
       <c r="F2577" s="0" t="s">
-        <v>9641</v>
+        <v>9642</v>
       </c>
     </row>
     <row r="2578" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2578" s="0" t="s">
-        <v>9642</v>
+        <v>9643</v>
       </c>
       <c r="B2578" s="0" t="s">
         <v>1417</v>
       </c>
       <c r="D2578" s="0" t="s">
-        <v>9631</v>
+        <v>9644</v>
       </c>
       <c r="E2578" s="0" t="s">
-        <v>9643</v>
+        <v>9645</v>
       </c>
       <c r="F2578" s="0" t="s">
-        <v>9633</v>
+        <v>9646</v>
       </c>
     </row>
     <row r="2579" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2579" s="0" t="s">
-        <v>9644</v>
+        <v>9647</v>
       </c>
       <c r="B2579" s="0" t="s">
         <v>1417</v>
       </c>
       <c r="D2579" s="0" t="s">
-        <v>9645</v>
+        <v>9636</v>
       </c>
       <c r="E2579" s="0" t="s">
-        <v>9646</v>
+        <v>9648</v>
       </c>
       <c r="F2579" s="0" t="s">
-        <v>9647</v>
+        <v>9638</v>
       </c>
     </row>
     <row r="2580" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2580" s="0" t="s">
-        <v>9648</v>
+        <v>9649</v>
       </c>
       <c r="B2580" s="0" t="s">
-        <v>9649</v>
+        <v>1417</v>
       </c>
       <c r="D2580" s="0" t="s">
         <v>9650</v>
@@ -81568,24 +81582,24 @@
         <v>9653</v>
       </c>
       <c r="B2581" s="0" t="s">
-        <v>7692</v>
+        <v>9654</v>
       </c>
       <c r="D2581" s="0" t="s">
-        <v>9654</v>
+        <v>9655</v>
       </c>
       <c r="E2581" s="0" t="s">
-        <v>9655</v>
+        <v>9656</v>
       </c>
       <c r="F2581" s="0" t="s">
-        <v>9656</v>
+        <v>9657</v>
       </c>
     </row>
     <row r="2582" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2582" s="0" t="s">
-        <v>9657</v>
+        <v>9658</v>
       </c>
       <c r="B2582" s="0" t="s">
-        <v>9658</v>
+        <v>7692</v>
       </c>
       <c r="D2582" s="0" t="s">
         <v>9659</v>
@@ -81602,710 +81616,710 @@
         <v>9662</v>
       </c>
       <c r="B2583" s="0" t="s">
-        <v>9658</v>
+        <v>9663</v>
       </c>
       <c r="D2583" s="0" t="s">
-        <v>9663</v>
+        <v>9664</v>
       </c>
       <c r="E2583" s="0" t="s">
-        <v>9664</v>
+        <v>9665</v>
       </c>
       <c r="F2583" s="0" t="s">
-        <v>9665</v>
+        <v>9666</v>
       </c>
     </row>
     <row r="2584" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2584" s="0" t="s">
-        <v>1</v>
+        <v>9667</v>
       </c>
       <c r="B2584" s="0" t="s">
-        <v>3045</v>
+        <v>9663</v>
       </c>
       <c r="D2584" s="0" t="s">
-        <v>3558</v>
+        <v>9668</v>
       </c>
       <c r="E2584" s="0" t="s">
-        <v>3559</v>
+        <v>9669</v>
       </c>
       <c r="F2584" s="0" t="s">
-        <v>3560</v>
+        <v>9670</v>
       </c>
     </row>
     <row r="2585" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2585" s="0" t="s">
-        <v>9666</v>
+        <v>1</v>
       </c>
       <c r="B2585" s="0" t="s">
         <v>3045</v>
       </c>
       <c r="D2585" s="0" t="s">
-        <v>9667</v>
+        <v>3558</v>
       </c>
       <c r="E2585" s="0" t="s">
-        <v>9668</v>
+        <v>3559</v>
       </c>
       <c r="F2585" s="0" t="s">
-        <v>9669</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="2586" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2586" s="0" t="s">
-        <v>9670</v>
+        <v>9671</v>
       </c>
       <c r="B2586" s="0" t="s">
         <v>3045</v>
       </c>
       <c r="D2586" s="0" t="s">
-        <v>9671</v>
+        <v>9672</v>
       </c>
       <c r="E2586" s="0" t="s">
-        <v>9672</v>
+        <v>9673</v>
       </c>
       <c r="F2586" s="0" t="s">
-        <v>9673</v>
+        <v>9674</v>
       </c>
     </row>
     <row r="2587" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2587" s="0" t="s">
-        <v>9674</v>
+        <v>9675</v>
       </c>
       <c r="B2587" s="0" t="s">
-        <v>1210</v>
+        <v>3045</v>
       </c>
       <c r="D2587" s="0" t="s">
-        <v>9675</v>
+        <v>9676</v>
       </c>
       <c r="E2587" s="0" t="s">
-        <v>9676</v>
+        <v>9677</v>
       </c>
       <c r="F2587" s="0" t="s">
-        <v>9677</v>
+        <v>9678</v>
       </c>
     </row>
     <row r="2588" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2588" s="0" t="s">
-        <v>9678</v>
+        <v>9679</v>
       </c>
       <c r="B2588" s="0" t="s">
-        <v>340</v>
+        <v>1210</v>
       </c>
       <c r="D2588" s="0" t="s">
-        <v>9679</v>
+        <v>9680</v>
       </c>
       <c r="E2588" s="0" t="s">
-        <v>9680</v>
+        <v>9681</v>
       </c>
       <c r="F2588" s="0" t="s">
-        <v>9681</v>
+        <v>9682</v>
       </c>
     </row>
     <row r="2589" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2589" s="0" t="s">
-        <v>9682</v>
+        <v>9683</v>
       </c>
       <c r="B2589" s="0" t="s">
-        <v>549</v>
+        <v>340</v>
       </c>
       <c r="D2589" s="0" t="s">
-        <v>9683</v>
+        <v>9684</v>
       </c>
       <c r="E2589" s="0" t="s">
-        <v>9684</v>
+        <v>9685</v>
       </c>
       <c r="F2589" s="0" t="s">
-        <v>9685</v>
+        <v>9686</v>
       </c>
     </row>
     <row r="2590" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2590" s="0" t="s">
-        <v>9686</v>
+        <v>9687</v>
       </c>
       <c r="B2590" s="0" t="s">
         <v>549</v>
       </c>
       <c r="D2590" s="0" t="s">
-        <v>9687</v>
+        <v>9688</v>
       </c>
       <c r="E2590" s="0" t="s">
-        <v>9688</v>
+        <v>9689</v>
       </c>
       <c r="F2590" s="0" t="s">
-        <v>9689</v>
+        <v>9690</v>
       </c>
     </row>
     <row r="2591" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2591" s="0" t="s">
-        <v>9690</v>
+        <v>9691</v>
       </c>
       <c r="B2591" s="0" t="s">
         <v>549</v>
       </c>
       <c r="D2591" s="0" t="s">
-        <v>9691</v>
+        <v>9692</v>
       </c>
       <c r="E2591" s="0" t="s">
-        <v>9692</v>
+        <v>9693</v>
       </c>
       <c r="F2591" s="0" t="s">
-        <v>9693</v>
+        <v>9694</v>
       </c>
     </row>
     <row r="2592" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2592" s="0" t="s">
-        <v>9694</v>
+        <v>9695</v>
       </c>
       <c r="B2592" s="0" t="s">
         <v>549</v>
       </c>
       <c r="D2592" s="0" t="s">
-        <v>9695</v>
+        <v>9696</v>
       </c>
       <c r="E2592" s="0" t="s">
-        <v>9696</v>
+        <v>9697</v>
       </c>
       <c r="F2592" s="0" t="s">
-        <v>9697</v>
+        <v>9698</v>
       </c>
     </row>
     <row r="2593" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2593" s="0" t="s">
-        <v>9698</v>
+        <v>9699</v>
       </c>
       <c r="B2593" s="0" t="s">
-        <v>3054</v>
+        <v>549</v>
       </c>
       <c r="D2593" s="0" t="s">
-        <v>9699</v>
+        <v>9700</v>
       </c>
       <c r="E2593" s="0" t="s">
-        <v>9700</v>
+        <v>9701</v>
       </c>
       <c r="F2593" s="0" t="s">
-        <v>9701</v>
+        <v>9702</v>
       </c>
     </row>
     <row r="2594" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2594" s="0" t="s">
-        <v>9702</v>
+        <v>9703</v>
       </c>
       <c r="B2594" s="0" t="s">
-        <v>549</v>
+        <v>3054</v>
       </c>
       <c r="D2594" s="0" t="s">
-        <v>8095</v>
+        <v>9704</v>
       </c>
       <c r="E2594" s="0" t="s">
-        <v>9703</v>
+        <v>9705</v>
       </c>
       <c r="F2594" s="0" t="s">
-        <v>9704</v>
+        <v>9706</v>
       </c>
     </row>
     <row r="2595" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2595" s="0" t="s">
-        <v>9705</v>
+        <v>9707</v>
       </c>
       <c r="B2595" s="0" t="s">
         <v>549</v>
       </c>
       <c r="D2595" s="0" t="s">
-        <v>9706</v>
+        <v>8095</v>
       </c>
       <c r="E2595" s="0" t="s">
-        <v>9707</v>
+        <v>9708</v>
       </c>
       <c r="F2595" s="0" t="s">
-        <v>9708</v>
+        <v>9709</v>
       </c>
     </row>
     <row r="2596" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2596" s="0" t="s">
-        <v>9709</v>
+        <v>9710</v>
       </c>
       <c r="B2596" s="0" t="s">
         <v>549</v>
       </c>
       <c r="D2596" s="0" t="s">
-        <v>9710</v>
+        <v>9711</v>
       </c>
       <c r="E2596" s="0" t="s">
-        <v>9711</v>
+        <v>9712</v>
       </c>
       <c r="F2596" s="0" t="s">
-        <v>9712</v>
+        <v>9713</v>
       </c>
     </row>
     <row r="2597" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2597" s="0" t="s">
-        <v>9713</v>
+        <v>9714</v>
       </c>
       <c r="B2597" s="0" t="s">
-        <v>8758</v>
+        <v>549</v>
       </c>
       <c r="D2597" s="0" t="s">
-        <v>9714</v>
+        <v>9715</v>
       </c>
       <c r="E2597" s="0" t="s">
-        <v>9715</v>
+        <v>9716</v>
       </c>
       <c r="F2597" s="0" t="s">
-        <v>9716</v>
+        <v>9717</v>
       </c>
     </row>
     <row r="2598" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2598" s="0" t="s">
-        <v>9717</v>
+        <v>9718</v>
       </c>
       <c r="B2598" s="0" t="s">
-        <v>549</v>
+        <v>8758</v>
       </c>
       <c r="D2598" s="0" t="s">
-        <v>9718</v>
+        <v>9719</v>
       </c>
       <c r="E2598" s="0" t="s">
-        <v>9719</v>
+        <v>9720</v>
       </c>
       <c r="F2598" s="0" t="s">
-        <v>9720</v>
+        <v>9721</v>
       </c>
     </row>
     <row r="2599" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2599" s="0" t="s">
-        <v>9721</v>
+        <v>9722</v>
       </c>
       <c r="B2599" s="0" t="s">
-        <v>4112</v>
+        <v>549</v>
       </c>
       <c r="D2599" s="0" t="s">
-        <v>9722</v>
+        <v>9723</v>
       </c>
       <c r="E2599" s="0" t="s">
-        <v>9723</v>
+        <v>9724</v>
       </c>
       <c r="F2599" s="0" t="s">
-        <v>9724</v>
+        <v>9725</v>
       </c>
     </row>
     <row r="2600" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2600" s="0" t="s">
-        <v>9725</v>
+        <v>9726</v>
       </c>
       <c r="B2600" s="0" t="s">
-        <v>664</v>
+        <v>4112</v>
       </c>
       <c r="D2600" s="0" t="s">
-        <v>9726</v>
+        <v>9727</v>
       </c>
       <c r="E2600" s="0" t="s">
-        <v>9727</v>
+        <v>9728</v>
       </c>
       <c r="F2600" s="0" t="s">
-        <v>9728</v>
+        <v>9729</v>
       </c>
     </row>
     <row r="2601" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2601" s="0" t="s">
-        <v>9729</v>
+        <v>9730</v>
       </c>
       <c r="B2601" s="0" t="s">
-        <v>2414</v>
+        <v>664</v>
       </c>
       <c r="D2601" s="0" t="s">
-        <v>9730</v>
+        <v>9731</v>
       </c>
       <c r="E2601" s="0" t="s">
-        <v>9731</v>
+        <v>9732</v>
       </c>
       <c r="F2601" s="0" t="s">
-        <v>9732</v>
+        <v>9733</v>
       </c>
     </row>
     <row r="2602" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2602" s="0" t="s">
-        <v>9733</v>
+        <v>9734</v>
       </c>
       <c r="B2602" s="0" t="s">
         <v>2414</v>
       </c>
       <c r="D2602" s="0" t="s">
-        <v>9734</v>
+        <v>9735</v>
       </c>
       <c r="E2602" s="0" t="s">
-        <v>9735</v>
+        <v>9736</v>
       </c>
       <c r="F2602" s="0" t="s">
-        <v>9736</v>
+        <v>9737</v>
       </c>
     </row>
     <row r="2603" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2603" s="0" t="s">
-        <v>9737</v>
+        <v>9738</v>
       </c>
       <c r="B2603" s="0" t="s">
         <v>2414</v>
       </c>
       <c r="D2603" s="0" t="s">
-        <v>9738</v>
+        <v>9739</v>
       </c>
       <c r="E2603" s="0" t="s">
-        <v>9739</v>
+        <v>9740</v>
       </c>
       <c r="F2603" s="0" t="s">
-        <v>9740</v>
+        <v>9741</v>
       </c>
     </row>
     <row r="2604" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2604" s="0" t="s">
-        <v>9741</v>
+        <v>9742</v>
       </c>
       <c r="B2604" s="0" t="s">
-        <v>664</v>
+        <v>2414</v>
       </c>
       <c r="D2604" s="0" t="s">
-        <v>9742</v>
+        <v>9743</v>
       </c>
       <c r="E2604" s="0" t="s">
-        <v>5349</v>
+        <v>9744</v>
       </c>
       <c r="F2604" s="0" t="s">
-        <v>9743</v>
+        <v>9745</v>
       </c>
     </row>
     <row r="2605" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2605" s="0" t="s">
-        <v>9744</v>
+        <v>9746</v>
       </c>
       <c r="B2605" s="0" t="s">
         <v>664</v>
       </c>
       <c r="D2605" s="0" t="s">
-        <v>9745</v>
+        <v>9747</v>
       </c>
       <c r="E2605" s="0" t="s">
-        <v>9746</v>
+        <v>5349</v>
       </c>
       <c r="F2605" s="0" t="s">
-        <v>9747</v>
+        <v>9748</v>
       </c>
     </row>
     <row r="2606" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2606" s="0" t="s">
-        <v>9748</v>
+        <v>9749</v>
       </c>
       <c r="B2606" s="0" t="s">
-        <v>1788</v>
-      </c>
-      <c r="C2606" s="0" t="s">
-        <v>6141</v>
+        <v>664</v>
       </c>
       <c r="D2606" s="0" t="s">
-        <v>9749</v>
+        <v>9750</v>
       </c>
       <c r="E2606" s="0" t="s">
-        <v>9750</v>
+        <v>9751</v>
       </c>
       <c r="F2606" s="0" t="s">
-        <v>9751</v>
+        <v>9752</v>
       </c>
     </row>
     <row r="2607" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2607" s="0" t="s">
-        <v>9752</v>
+        <v>9753</v>
       </c>
       <c r="B2607" s="0" t="s">
-        <v>664</v>
+        <v>1788</v>
       </c>
       <c r="C2607" s="0" t="s">
         <v>6141</v>
       </c>
       <c r="D2607" s="0" t="s">
-        <v>9753</v>
+        <v>9754</v>
       </c>
       <c r="E2607" s="0" t="s">
-        <v>9753</v>
+        <v>9755</v>
       </c>
       <c r="F2607" s="0" t="s">
-        <v>9753</v>
+        <v>9756</v>
       </c>
     </row>
     <row r="2608" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2608" s="0" t="s">
-        <v>9754</v>
+        <v>9757</v>
       </c>
       <c r="B2608" s="0" t="s">
         <v>664</v>
       </c>
+      <c r="C2608" s="0" t="s">
+        <v>6141</v>
+      </c>
       <c r="D2608" s="0" t="s">
-        <v>9755</v>
+        <v>9758</v>
       </c>
       <c r="E2608" s="0" t="s">
-        <v>9756</v>
+        <v>9758</v>
       </c>
       <c r="F2608" s="0" t="s">
-        <v>9757</v>
+        <v>9758</v>
       </c>
     </row>
     <row r="2609" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2609" s="0" t="s">
-        <v>9758</v>
+        <v>9759</v>
       </c>
       <c r="B2609" s="0" t="s">
         <v>664</v>
       </c>
       <c r="D2609" s="0" t="s">
-        <v>9759</v>
+        <v>9760</v>
       </c>
       <c r="E2609" s="0" t="s">
-        <v>9760</v>
+        <v>9761</v>
       </c>
       <c r="F2609" s="0" t="s">
-        <v>9761</v>
-      </c>
-    </row>
-    <row r="2610" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>9762</v>
+      </c>
+    </row>
+    <row r="2610" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2610" s="0" t="s">
-        <v>9762</v>
+        <v>9763</v>
       </c>
       <c r="B2610" s="0" t="s">
+        <v>664</v>
+      </c>
+      <c r="D2610" s="0" t="s">
+        <v>9764</v>
+      </c>
+      <c r="E2610" s="0" t="s">
+        <v>9765</v>
+      </c>
+      <c r="F2610" s="0" t="s">
+        <v>9766</v>
+      </c>
+    </row>
+    <row r="2611" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2611" s="0" t="s">
+        <v>9767</v>
+      </c>
+      <c r="B2611" s="0" t="s">
         <v>624</v>
       </c>
-      <c r="D2610" s="2" t="s">
-        <v>9763</v>
-      </c>
-      <c r="E2610" s="2" t="s">
-        <v>9764</v>
-      </c>
-      <c r="F2610" s="2" t="s">
-        <v>9765</v>
-      </c>
-    </row>
-    <row r="2611" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2611" s="0" t="s">
-        <v>9766</v>
-      </c>
-      <c r="B2611" s="0" t="s">
-        <v>1914</v>
-      </c>
-      <c r="D2611" s="0" t="s">
-        <v>9767</v>
-      </c>
-      <c r="E2611" s="0" t="s">
+      <c r="D2611" s="2" t="s">
         <v>9768</v>
       </c>
-      <c r="F2611" s="0" t="s">
+      <c r="E2611" s="2" t="s">
         <v>9769</v>
+      </c>
+      <c r="F2611" s="2" t="s">
+        <v>9770</v>
       </c>
     </row>
     <row r="2612" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2612" s="0" t="s">
-        <v>9770</v>
+        <v>9771</v>
       </c>
       <c r="B2612" s="0" t="s">
-        <v>4165</v>
+        <v>1914</v>
       </c>
       <c r="D2612" s="0" t="s">
-        <v>9771</v>
+        <v>9772</v>
       </c>
       <c r="E2612" s="0" t="s">
-        <v>9772</v>
+        <v>9773</v>
       </c>
       <c r="F2612" s="0" t="s">
-        <v>9773</v>
+        <v>9774</v>
       </c>
     </row>
     <row r="2613" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2613" s="0" t="s">
-        <v>9774</v>
+        <v>9775</v>
       </c>
       <c r="B2613" s="0" t="s">
         <v>4165</v>
       </c>
       <c r="D2613" s="0" t="s">
-        <v>9775</v>
+        <v>9776</v>
       </c>
       <c r="E2613" s="0" t="s">
-        <v>9776</v>
+        <v>9777</v>
       </c>
       <c r="F2613" s="0" t="s">
-        <v>9777</v>
+        <v>9778</v>
       </c>
     </row>
     <row r="2614" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2614" s="0" t="s">
-        <v>9778</v>
+        <v>9779</v>
       </c>
       <c r="B2614" s="0" t="s">
-        <v>650</v>
+        <v>4165</v>
       </c>
       <c r="D2614" s="0" t="s">
-        <v>9779</v>
+        <v>9780</v>
       </c>
       <c r="E2614" s="0" t="s">
-        <v>9780</v>
+        <v>9781</v>
       </c>
       <c r="F2614" s="0" t="s">
-        <v>9781</v>
+        <v>9782</v>
       </c>
     </row>
     <row r="2615" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2615" s="0" t="s">
-        <v>9782</v>
+        <v>9783</v>
       </c>
       <c r="B2615" s="0" t="s">
         <v>650</v>
       </c>
       <c r="D2615" s="0" t="s">
-        <v>9783</v>
+        <v>9784</v>
       </c>
       <c r="E2615" s="0" t="s">
-        <v>9784</v>
+        <v>9785</v>
       </c>
       <c r="F2615" s="0" t="s">
-        <v>9785</v>
+        <v>9786</v>
       </c>
     </row>
     <row r="2616" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2616" s="0" t="s">
-        <v>9786</v>
+        <v>9787</v>
       </c>
       <c r="B2616" s="0" t="s">
         <v>650</v>
       </c>
       <c r="D2616" s="0" t="s">
-        <v>9787</v>
+        <v>9788</v>
       </c>
       <c r="E2616" s="0" t="s">
-        <v>9788</v>
+        <v>9789</v>
       </c>
       <c r="F2616" s="0" t="s">
-        <v>9789</v>
+        <v>9790</v>
       </c>
     </row>
     <row r="2617" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2617" s="0" t="s">
-        <v>9790</v>
+        <v>9791</v>
       </c>
       <c r="B2617" s="0" t="s">
-        <v>9531</v>
+        <v>650</v>
       </c>
       <c r="D2617" s="0" t="s">
-        <v>9791</v>
+        <v>9792</v>
       </c>
       <c r="E2617" s="0" t="s">
-        <v>9792</v>
+        <v>9793</v>
       </c>
       <c r="F2617" s="0" t="s">
-        <v>9793</v>
+        <v>9794</v>
       </c>
     </row>
     <row r="2618" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2618" s="0" t="s">
-        <v>9794</v>
+        <v>9795</v>
       </c>
       <c r="B2618" s="0" t="s">
-        <v>340</v>
+        <v>9536</v>
       </c>
       <c r="D2618" s="0" t="s">
-        <v>9795</v>
+        <v>9796</v>
       </c>
       <c r="E2618" s="0" t="s">
-        <v>9796</v>
+        <v>9797</v>
       </c>
       <c r="F2618" s="0" t="s">
-        <v>9797</v>
+        <v>9798</v>
       </c>
     </row>
     <row r="2619" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2619" s="0" t="s">
-        <v>9798</v>
+        <v>9799</v>
       </c>
       <c r="B2619" s="0" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D2619" s="0" t="s">
-        <v>9799</v>
+        <v>9800</v>
       </c>
       <c r="E2619" s="0" t="s">
-        <v>9799</v>
+        <v>9801</v>
       </c>
       <c r="F2619" s="0" t="s">
-        <v>9799</v>
+        <v>9802</v>
       </c>
     </row>
     <row r="2620" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2620" s="0" t="s">
-        <v>9800</v>
+        <v>9803</v>
       </c>
       <c r="B2620" s="0" t="s">
         <v>345</v>
       </c>
       <c r="D2620" s="0" t="s">
-        <v>9801</v>
+        <v>9804</v>
       </c>
       <c r="E2620" s="0" t="s">
-        <v>9802</v>
+        <v>9804</v>
       </c>
       <c r="F2620" s="0" t="s">
-        <v>9803</v>
+        <v>9804</v>
       </c>
     </row>
     <row r="2621" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2621" s="0" t="s">
-        <v>9804</v>
+        <v>9805</v>
       </c>
       <c r="B2621" s="0" t="s">
-        <v>9805</v>
+        <v>345</v>
       </c>
       <c r="D2621" s="0" t="s">
         <v>9806</v>
       </c>
       <c r="E2621" s="0" t="s">
-        <v>7652</v>
+        <v>9807</v>
       </c>
       <c r="F2621" s="0" t="s">
-        <v>9807</v>
+        <v>9808</v>
       </c>
     </row>
     <row r="2622" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2622" s="0" t="s">
-        <v>9808</v>
+        <v>9809</v>
       </c>
       <c r="B2622" s="0" t="s">
-        <v>9805</v>
+        <v>9810</v>
       </c>
       <c r="D2622" s="0" t="s">
-        <v>9809</v>
+        <v>9811</v>
       </c>
       <c r="E2622" s="0" t="s">
-        <v>9810</v>
+        <v>7652</v>
       </c>
       <c r="F2622" s="0" t="s">
-        <v>9811</v>
+        <v>9812</v>
       </c>
     </row>
     <row r="2623" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2623" s="0" t="s">
-        <v>9812</v>
+        <v>9813</v>
       </c>
       <c r="B2623" s="0" t="s">
-        <v>3625</v>
+        <v>9810</v>
       </c>
       <c r="D2623" s="0" t="s">
-        <v>9813</v>
+        <v>9814</v>
       </c>
       <c r="E2623" s="0" t="s">
-        <v>9814</v>
+        <v>9815</v>
       </c>
       <c r="F2623" s="0" t="s">
-        <v>9815</v>
+        <v>9816</v>
       </c>
     </row>
     <row r="2624" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2624" s="0" t="s">
-        <v>9816</v>
+        <v>9817</v>
       </c>
       <c r="B2624" s="0" t="s">
-        <v>9817</v>
+        <v>3625</v>
       </c>
       <c r="D2624" s="0" t="s">
         <v>9818</v>
@@ -82322,41 +82336,41 @@
         <v>9821</v>
       </c>
       <c r="B2625" s="0" t="s">
-        <v>9817</v>
+        <v>9822</v>
       </c>
       <c r="D2625" s="0" t="s">
-        <v>9822</v>
+        <v>9823</v>
       </c>
       <c r="E2625" s="0" t="s">
-        <v>9823</v>
+        <v>9824</v>
       </c>
       <c r="F2625" s="0" t="s">
-        <v>9824</v>
+        <v>9825</v>
       </c>
     </row>
     <row r="2626" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2626" s="0" t="s">
-        <v>9825</v>
+        <v>9826</v>
       </c>
       <c r="B2626" s="0" t="s">
-        <v>9817</v>
+        <v>9822</v>
       </c>
       <c r="D2626" s="0" t="s">
-        <v>9826</v>
+        <v>9827</v>
       </c>
       <c r="E2626" s="0" t="s">
-        <v>9827</v>
+        <v>9828</v>
       </c>
       <c r="F2626" s="0" t="s">
-        <v>9828</v>
+        <v>9829</v>
       </c>
     </row>
     <row r="2627" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2627" s="0" t="s">
-        <v>9829</v>
+        <v>9830</v>
       </c>
       <c r="B2627" s="0" t="s">
-        <v>9830</v>
+        <v>9822</v>
       </c>
       <c r="D2627" s="0" t="s">
         <v>9831</v>
@@ -82373,109 +82387,109 @@
         <v>9834</v>
       </c>
       <c r="B2628" s="0" t="s">
-        <v>4285</v>
+        <v>9835</v>
       </c>
       <c r="D2628" s="0" t="s">
-        <v>9835</v>
+        <v>9836</v>
       </c>
       <c r="E2628" s="0" t="s">
-        <v>9836</v>
+        <v>9837</v>
       </c>
       <c r="F2628" s="0" t="s">
-        <v>9837</v>
+        <v>9838</v>
       </c>
     </row>
     <row r="2629" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2629" s="0" t="s">
-        <v>9838</v>
+        <v>9839</v>
       </c>
       <c r="B2629" s="0" t="s">
         <v>4285</v>
       </c>
       <c r="D2629" s="0" t="s">
-        <v>9839</v>
+        <v>9840</v>
       </c>
       <c r="E2629" s="0" t="s">
-        <v>9840</v>
+        <v>9841</v>
       </c>
       <c r="F2629" s="0" t="s">
-        <v>9841</v>
+        <v>9842</v>
       </c>
     </row>
     <row r="2630" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2630" s="0" t="s">
-        <v>9842</v>
+        <v>9843</v>
       </c>
       <c r="B2630" s="0" t="s">
+        <v>4285</v>
+      </c>
+      <c r="D2630" s="0" t="s">
+        <v>9844</v>
+      </c>
+      <c r="E2630" s="0" t="s">
+        <v>9845</v>
+      </c>
+      <c r="F2630" s="0" t="s">
+        <v>9846</v>
+      </c>
+    </row>
+    <row r="2631" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2631" s="0" t="s">
+        <v>9847</v>
+      </c>
+      <c r="B2631" s="0" t="s">
         <v>952</v>
       </c>
-      <c r="D2630" s="0" t="s">
-        <v>9843</v>
-      </c>
-      <c r="E2630" s="0" t="s">
-        <v>9844</v>
-      </c>
-      <c r="F2630" s="0" t="s">
-        <v>9845</v>
-      </c>
-    </row>
-    <row r="2631" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2631" s="0" t="s">
-        <v>9846</v>
-      </c>
-      <c r="B2631" s="0" t="s">
-        <v>350</v>
-      </c>
-      <c r="D2631" s="2" t="s">
-        <v>9847</v>
-      </c>
-      <c r="E2631" s="2" t="s">
+      <c r="D2631" s="0" t="s">
         <v>9848</v>
       </c>
-      <c r="F2631" s="2" t="s">
+      <c r="E2631" s="0" t="s">
         <v>9849</v>
       </c>
-    </row>
-    <row r="2632" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2631" s="0" t="s">
+        <v>9850</v>
+      </c>
+    </row>
+    <row r="2632" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2632" s="0" t="s">
-        <v>9850</v>
+        <v>9851</v>
       </c>
       <c r="B2632" s="0" t="s">
         <v>350</v>
       </c>
-      <c r="D2632" s="0" t="s">
-        <v>9851</v>
-      </c>
-      <c r="E2632" s="0" t="s">
+      <c r="D2632" s="2" t="s">
         <v>9852</v>
       </c>
-      <c r="F2632" s="0" t="s">
+      <c r="E2632" s="2" t="s">
         <v>9853</v>
+      </c>
+      <c r="F2632" s="2" t="s">
+        <v>9854</v>
       </c>
     </row>
     <row r="2633" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2633" s="0" t="s">
-        <v>9854</v>
+        <v>9855</v>
       </c>
       <c r="B2633" s="0" t="s">
         <v>350</v>
       </c>
       <c r="D2633" s="0" t="s">
-        <v>9855</v>
+        <v>9856</v>
       </c>
       <c r="E2633" s="0" t="s">
-        <v>9856</v>
+        <v>9857</v>
       </c>
       <c r="F2633" s="0" t="s">
-        <v>9857</v>
+        <v>9858</v>
       </c>
     </row>
     <row r="2634" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2634" s="0" t="s">
-        <v>9858</v>
+        <v>9859</v>
       </c>
       <c r="B2634" s="0" t="s">
-        <v>9859</v>
+        <v>350</v>
       </c>
       <c r="D2634" s="0" t="s">
         <v>9860</v>
@@ -82492,928 +82506,925 @@
         <v>9863</v>
       </c>
       <c r="B2635" s="0" t="s">
-        <v>350</v>
+        <v>9864</v>
       </c>
       <c r="D2635" s="0" t="s">
-        <v>9864</v>
+        <v>9865</v>
       </c>
       <c r="E2635" s="0" t="s">
-        <v>9856</v>
+        <v>9866</v>
       </c>
       <c r="F2635" s="0" t="s">
-        <v>9865</v>
+        <v>9867</v>
       </c>
     </row>
     <row r="2636" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2636" s="0" t="s">
-        <v>9866</v>
+        <v>9868</v>
       </c>
       <c r="B2636" s="0" t="s">
         <v>350</v>
       </c>
       <c r="D2636" s="0" t="s">
-        <v>9867</v>
+        <v>9869</v>
       </c>
       <c r="E2636" s="0" t="s">
-        <v>9868</v>
+        <v>9861</v>
       </c>
       <c r="F2636" s="0" t="s">
-        <v>9869</v>
+        <v>9870</v>
       </c>
     </row>
     <row r="2637" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2637" s="0" t="s">
-        <v>9870</v>
+        <v>9871</v>
       </c>
       <c r="B2637" s="0" t="s">
-        <v>19</v>
+        <v>350</v>
       </c>
       <c r="D2637" s="0" t="s">
-        <v>9871</v>
+        <v>9872</v>
       </c>
       <c r="E2637" s="0" t="s">
-        <v>9872</v>
+        <v>9873</v>
       </c>
       <c r="F2637" s="0" t="s">
-        <v>9873</v>
+        <v>9874</v>
       </c>
     </row>
     <row r="2638" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2638" s="0" t="s">
-        <v>9874</v>
+        <v>9875</v>
       </c>
       <c r="B2638" s="0" t="s">
         <v>19</v>
       </c>
       <c r="D2638" s="0" t="s">
-        <v>9875</v>
+        <v>9876</v>
       </c>
       <c r="E2638" s="0" t="s">
-        <v>9876</v>
+        <v>9877</v>
       </c>
       <c r="F2638" s="0" t="s">
-        <v>9877</v>
+        <v>9878</v>
       </c>
     </row>
     <row r="2639" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2639" s="0" t="s">
-        <v>9878</v>
+        <v>9879</v>
       </c>
       <c r="B2639" s="0" t="s">
-        <v>350</v>
+        <v>19</v>
       </c>
       <c r="D2639" s="0" t="s">
-        <v>9879</v>
+        <v>9880</v>
       </c>
       <c r="E2639" s="0" t="s">
-        <v>9880</v>
+        <v>9881</v>
       </c>
       <c r="F2639" s="0" t="s">
-        <v>9881</v>
+        <v>9882</v>
       </c>
     </row>
     <row r="2640" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2640" s="0" t="s">
-        <v>9882</v>
+        <v>9883</v>
       </c>
       <c r="B2640" s="0" t="s">
         <v>350</v>
       </c>
       <c r="D2640" s="0" t="s">
-        <v>9883</v>
+        <v>9884</v>
       </c>
       <c r="E2640" s="0" t="s">
-        <v>9884</v>
+        <v>9885</v>
       </c>
       <c r="F2640" s="0" t="s">
-        <v>9885</v>
+        <v>9886</v>
       </c>
     </row>
     <row r="2641" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2641" s="0" t="s">
-        <v>9886</v>
+        <v>9887</v>
       </c>
       <c r="B2641" s="0" t="s">
         <v>350</v>
       </c>
       <c r="D2641" s="0" t="s">
-        <v>9887</v>
+        <v>9888</v>
       </c>
       <c r="E2641" s="0" t="s">
-        <v>9888</v>
+        <v>9889</v>
       </c>
       <c r="F2641" s="0" t="s">
-        <v>9889</v>
+        <v>9890</v>
       </c>
     </row>
     <row r="2642" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2642" s="0" t="s">
-        <v>9890</v>
+        <v>9891</v>
       </c>
       <c r="B2642" s="0" t="s">
         <v>350</v>
       </c>
       <c r="D2642" s="0" t="s">
-        <v>7221</v>
+        <v>9892</v>
       </c>
       <c r="E2642" s="0" t="s">
-        <v>7222</v>
+        <v>9893</v>
       </c>
       <c r="F2642" s="0" t="s">
-        <v>7223</v>
+        <v>9894</v>
       </c>
     </row>
     <row r="2643" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2643" s="0" t="s">
-        <v>9891</v>
+        <v>9895</v>
       </c>
       <c r="B2643" s="0" t="s">
         <v>350</v>
       </c>
       <c r="D2643" s="0" t="s">
-        <v>9892</v>
+        <v>7221</v>
       </c>
       <c r="E2643" s="0" t="s">
-        <v>9893</v>
+        <v>7222</v>
       </c>
       <c r="F2643" s="0" t="s">
-        <v>9894</v>
+        <v>7223</v>
       </c>
     </row>
     <row r="2644" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2644" s="0" t="s">
-        <v>9895</v>
+        <v>9896</v>
       </c>
       <c r="B2644" s="0" t="s">
-        <v>1327</v>
+        <v>350</v>
       </c>
       <c r="D2644" s="0" t="s">
-        <v>9896</v>
+        <v>9897</v>
       </c>
       <c r="E2644" s="0" t="s">
-        <v>9897</v>
+        <v>9898</v>
       </c>
       <c r="F2644" s="0" t="s">
-        <v>9898</v>
+        <v>9899</v>
       </c>
     </row>
     <row r="2645" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2645" s="0" t="s">
-        <v>9899</v>
+        <v>9900</v>
       </c>
       <c r="B2645" s="0" t="s">
-        <v>16</v>
+        <v>1327</v>
       </c>
       <c r="D2645" s="0" t="s">
-        <v>9900</v>
+        <v>9901</v>
       </c>
       <c r="E2645" s="0" t="s">
-        <v>9901</v>
+        <v>9902</v>
       </c>
       <c r="F2645" s="0" t="s">
-        <v>9902</v>
+        <v>9903</v>
       </c>
     </row>
     <row r="2646" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2646" s="0" t="s">
-        <v>9903</v>
+        <v>9904</v>
       </c>
       <c r="B2646" s="0" t="s">
         <v>16</v>
       </c>
       <c r="D2646" s="0" t="s">
-        <v>9904</v>
+        <v>9905</v>
       </c>
       <c r="E2646" s="0" t="s">
-        <v>9905</v>
+        <v>9906</v>
       </c>
       <c r="F2646" s="0" t="s">
-        <v>9906</v>
+        <v>9907</v>
       </c>
     </row>
     <row r="2647" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2647" s="0" t="s">
-        <v>9907</v>
+        <v>9908</v>
       </c>
       <c r="B2647" s="0" t="s">
         <v>16</v>
       </c>
       <c r="D2647" s="0" t="s">
-        <v>9908</v>
+        <v>9909</v>
       </c>
       <c r="E2647" s="0" t="s">
-        <v>9909</v>
+        <v>9910</v>
       </c>
       <c r="F2647" s="0" t="s">
-        <v>9910</v>
+        <v>9911</v>
       </c>
     </row>
     <row r="2648" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2648" s="0" t="s">
-        <v>9911</v>
+        <v>9912</v>
       </c>
       <c r="B2648" s="0" t="s">
         <v>16</v>
       </c>
       <c r="D2648" s="0" t="s">
-        <v>9912</v>
+        <v>9913</v>
       </c>
       <c r="E2648" s="0" t="s">
-        <v>9913</v>
+        <v>9914</v>
       </c>
       <c r="F2648" s="0" t="s">
-        <v>9914</v>
+        <v>9915</v>
       </c>
     </row>
     <row r="2649" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2649" s="0" t="s">
-        <v>9915</v>
+        <v>9916</v>
       </c>
       <c r="B2649" s="0" t="s">
         <v>16</v>
       </c>
       <c r="D2649" s="0" t="s">
-        <v>9916</v>
+        <v>9917</v>
       </c>
       <c r="E2649" s="0" t="s">
-        <v>9917</v>
+        <v>9918</v>
       </c>
       <c r="F2649" s="0" t="s">
-        <v>9918</v>
+        <v>9919</v>
       </c>
     </row>
     <row r="2650" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2650" s="0" t="s">
-        <v>9919</v>
+        <v>9920</v>
       </c>
       <c r="B2650" s="0" t="s">
         <v>16</v>
       </c>
       <c r="D2650" s="0" t="s">
-        <v>9920</v>
+        <v>9921</v>
       </c>
       <c r="E2650" s="0" t="s">
-        <v>9921</v>
+        <v>9922</v>
       </c>
       <c r="F2650" s="0" t="s">
-        <v>9922</v>
+        <v>9923</v>
       </c>
     </row>
     <row r="2651" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2651" s="0" t="s">
-        <v>9923</v>
+        <v>9924</v>
       </c>
       <c r="B2651" s="0" t="s">
         <v>16</v>
       </c>
       <c r="D2651" s="0" t="s">
-        <v>9924</v>
+        <v>9925</v>
       </c>
       <c r="E2651" s="0" t="s">
-        <v>9925</v>
+        <v>9926</v>
       </c>
       <c r="F2651" s="0" t="s">
-        <v>9926</v>
+        <v>9927</v>
       </c>
     </row>
     <row r="2652" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2652" s="0" t="s">
-        <v>9927</v>
+        <v>9928</v>
       </c>
       <c r="B2652" s="0" t="s">
-        <v>624</v>
+        <v>16</v>
       </c>
       <c r="D2652" s="0" t="s">
-        <v>9928</v>
+        <v>9929</v>
       </c>
       <c r="E2652" s="0" t="s">
-        <v>9929</v>
+        <v>9930</v>
       </c>
       <c r="F2652" s="0" t="s">
-        <v>9930</v>
+        <v>9931</v>
       </c>
     </row>
     <row r="2653" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2653" s="0" t="s">
-        <v>9931</v>
+        <v>9932</v>
       </c>
       <c r="B2653" s="0" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="D2653" s="0" t="s">
-        <v>9932</v>
+        <v>9933</v>
       </c>
       <c r="E2653" s="0" t="s">
-        <v>9933</v>
+        <v>9934</v>
       </c>
       <c r="F2653" s="0" t="s">
-        <v>9934</v>
-      </c>
-    </row>
-    <row r="2654" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>9935</v>
+      </c>
+    </row>
+    <row r="2654" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2654" s="0" t="s">
-        <v>9935</v>
+        <v>9936</v>
       </c>
       <c r="B2654" s="0" t="s">
         <v>619</v>
       </c>
-      <c r="D2654" s="2" t="s">
-        <v>9936</v>
-      </c>
-      <c r="E2654" s="2" t="s">
+      <c r="D2654" s="0" t="s">
         <v>9937</v>
       </c>
-      <c r="F2654" s="2" t="s">
+      <c r="E2654" s="0" t="s">
         <v>9938</v>
       </c>
-    </row>
-    <row r="2655" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2654" s="0" t="s">
+        <v>9939</v>
+      </c>
+    </row>
+    <row r="2655" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2655" s="0" t="s">
-        <v>9939</v>
+        <v>9940</v>
       </c>
       <c r="B2655" s="0" t="s">
-        <v>19</v>
+        <v>619</v>
       </c>
       <c r="D2655" s="2" t="s">
-        <v>9940</v>
+        <v>9941</v>
       </c>
       <c r="E2655" s="2" t="s">
-        <v>9941</v>
+        <v>9942</v>
       </c>
       <c r="F2655" s="2" t="s">
-        <v>9942</v>
-      </c>
-    </row>
-    <row r="2656" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>9943</v>
+      </c>
+    </row>
+    <row r="2656" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2656" s="0" t="s">
-        <v>9943</v>
+        <v>9944</v>
       </c>
       <c r="B2656" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D2656" s="0" t="s">
-        <v>9944</v>
-      </c>
-      <c r="E2656" s="0" t="s">
+      <c r="D2656" s="2" t="s">
         <v>9945</v>
       </c>
-      <c r="F2656" s="0" t="s">
+      <c r="E2656" s="2" t="s">
         <v>9946</v>
       </c>
-    </row>
-    <row r="2657" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2656" s="2" t="s">
+        <v>9947</v>
+      </c>
+    </row>
+    <row r="2657" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2657" s="0" t="s">
-        <v>9947</v>
+        <v>9948</v>
       </c>
       <c r="B2657" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D2657" s="2" t="s">
-        <v>9948</v>
-      </c>
-      <c r="E2657" s="2" t="s">
+      <c r="D2657" s="0" t="s">
         <v>9949</v>
       </c>
-      <c r="F2657" s="2" t="s">
+      <c r="E2657" s="0" t="s">
         <v>9950</v>
       </c>
-    </row>
-    <row r="2658" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2657" s="0" t="s">
+        <v>9951</v>
+      </c>
+    </row>
+    <row r="2658" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2658" s="0" t="s">
-        <v>9951</v>
+        <v>9952</v>
       </c>
       <c r="B2658" s="0" t="s">
-        <v>1828</v>
-      </c>
-      <c r="D2658" s="0" t="s">
-        <v>2614</v>
-      </c>
-      <c r="E2658" s="0" t="s">
-        <v>2615</v>
-      </c>
-      <c r="F2658" s="0" t="s">
-        <v>2616</v>
+        <v>19</v>
+      </c>
+      <c r="D2658" s="2" t="s">
+        <v>9953</v>
+      </c>
+      <c r="E2658" s="2" t="s">
+        <v>9954</v>
+      </c>
+      <c r="F2658" s="2" t="s">
+        <v>9955</v>
       </c>
     </row>
     <row r="2659" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2659" s="0" t="s">
-        <v>9952</v>
+        <v>9956</v>
       </c>
       <c r="B2659" s="0" t="s">
         <v>1828</v>
       </c>
       <c r="D2659" s="0" t="s">
-        <v>9953</v>
+        <v>2614</v>
       </c>
       <c r="E2659" s="0" t="s">
-        <v>9954</v>
+        <v>2615</v>
       </c>
       <c r="F2659" s="0" t="s">
-        <v>9955</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="2660" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2660" s="0" t="s">
-        <v>9956</v>
+        <v>9957</v>
       </c>
       <c r="B2660" s="0" t="s">
         <v>1828</v>
       </c>
       <c r="D2660" s="0" t="s">
-        <v>9957</v>
+        <v>9958</v>
       </c>
       <c r="E2660" s="0" t="s">
-        <v>9958</v>
+        <v>9959</v>
       </c>
       <c r="F2660" s="0" t="s">
-        <v>9959</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="2661" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2661" s="0" t="s">
-        <v>9960</v>
+        <v>9961</v>
       </c>
       <c r="B2661" s="0" t="s">
         <v>1828</v>
       </c>
       <c r="D2661" s="0" t="s">
-        <v>9961</v>
+        <v>9962</v>
       </c>
       <c r="E2661" s="0" t="s">
-        <v>9962</v>
+        <v>9963</v>
       </c>
       <c r="F2661" s="0" t="s">
-        <v>9963</v>
+        <v>9964</v>
       </c>
     </row>
     <row r="2662" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2662" s="0" t="s">
-        <v>9964</v>
+        <v>9965</v>
       </c>
       <c r="B2662" s="0" t="s">
         <v>1828</v>
       </c>
       <c r="D2662" s="0" t="s">
-        <v>9965</v>
+        <v>9966</v>
       </c>
       <c r="E2662" s="0" t="s">
-        <v>9966</v>
+        <v>9967</v>
       </c>
       <c r="F2662" s="0" t="s">
-        <v>9967</v>
+        <v>9968</v>
       </c>
     </row>
     <row r="2663" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2663" s="0" t="s">
-        <v>9968</v>
+        <v>9969</v>
       </c>
       <c r="B2663" s="0" t="s">
-        <v>3054</v>
+        <v>1828</v>
       </c>
       <c r="D2663" s="0" t="s">
-        <v>9969</v>
+        <v>9970</v>
       </c>
       <c r="E2663" s="0" t="s">
-        <v>9970</v>
+        <v>9971</v>
       </c>
       <c r="F2663" s="0" t="s">
-        <v>9971</v>
+        <v>9972</v>
       </c>
     </row>
     <row r="2664" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2664" s="0" t="s">
-        <v>9972</v>
+        <v>9973</v>
       </c>
       <c r="B2664" s="0" t="s">
-        <v>1828</v>
+        <v>3054</v>
       </c>
       <c r="D2664" s="0" t="s">
-        <v>9973</v>
+        <v>9974</v>
       </c>
       <c r="E2664" s="0" t="s">
-        <v>9974</v>
+        <v>9975</v>
       </c>
       <c r="F2664" s="0" t="s">
-        <v>9975</v>
+        <v>9976</v>
       </c>
     </row>
     <row r="2665" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2665" s="0" t="s">
-        <v>9976</v>
+        <v>9977</v>
       </c>
       <c r="B2665" s="0" t="s">
         <v>1828</v>
       </c>
       <c r="D2665" s="0" t="s">
-        <v>9977</v>
+        <v>9978</v>
       </c>
       <c r="E2665" s="0" t="s">
-        <v>9978</v>
+        <v>9979</v>
       </c>
       <c r="F2665" s="0" t="s">
-        <v>9979</v>
+        <v>9980</v>
       </c>
     </row>
     <row r="2666" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2666" s="0" t="s">
-        <v>9980</v>
+        <v>9981</v>
       </c>
       <c r="B2666" s="0" t="s">
-        <v>689</v>
+        <v>1828</v>
       </c>
       <c r="D2666" s="0" t="s">
-        <v>9981</v>
+        <v>9982</v>
       </c>
       <c r="E2666" s="0" t="s">
-        <v>9982</v>
+        <v>9983</v>
       </c>
       <c r="F2666" s="0" t="s">
-        <v>9983</v>
-      </c>
-    </row>
-    <row r="2667" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>9984</v>
+      </c>
+    </row>
+    <row r="2667" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2667" s="0" t="s">
-        <v>9984</v>
+        <v>9985</v>
       </c>
       <c r="B2667" s="0" t="s">
         <v>689</v>
       </c>
-      <c r="D2667" s="2" t="s">
-        <v>9985</v>
-      </c>
-      <c r="E2667" s="2" t="s">
+      <c r="D2667" s="0" t="s">
         <v>9986</v>
       </c>
-      <c r="F2667" s="2" t="s">
+      <c r="E2667" s="0" t="s">
         <v>9987</v>
       </c>
-    </row>
-    <row r="2668" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2667" s="0" t="s">
+        <v>9988</v>
+      </c>
+    </row>
+    <row r="2668" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2668" s="0" t="s">
-        <v>9988</v>
+        <v>9989</v>
       </c>
       <c r="B2668" s="0" t="s">
-        <v>1828</v>
-      </c>
-      <c r="D2668" s="0" t="s">
-        <v>9989</v>
-      </c>
-      <c r="E2668" s="0" t="s">
+        <v>689</v>
+      </c>
+      <c r="D2668" s="2" t="s">
         <v>9990</v>
       </c>
-      <c r="F2668" s="0" t="s">
+      <c r="E2668" s="2" t="s">
         <v>9991</v>
+      </c>
+      <c r="F2668" s="2" t="s">
+        <v>9992</v>
       </c>
     </row>
     <row r="2669" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2669" s="0" t="s">
-        <v>9992</v>
+        <v>9993</v>
       </c>
       <c r="B2669" s="0" t="s">
         <v>1828</v>
       </c>
       <c r="D2669" s="0" t="s">
-        <v>9993</v>
+        <v>9994</v>
       </c>
       <c r="E2669" s="0" t="s">
-        <v>9994</v>
+        <v>9995</v>
       </c>
       <c r="F2669" s="0" t="s">
-        <v>9995</v>
+        <v>9996</v>
       </c>
     </row>
     <row r="2670" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2670" s="0" t="s">
-        <v>9996</v>
+        <v>9997</v>
       </c>
       <c r="B2670" s="0" t="s">
         <v>1828</v>
       </c>
       <c r="D2670" s="0" t="s">
-        <v>9997</v>
+        <v>9998</v>
       </c>
       <c r="E2670" s="0" t="s">
-        <v>9998</v>
+        <v>9999</v>
       </c>
       <c r="F2670" s="0" t="s">
-        <v>9999</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="2671" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2671" s="0" t="s">
-        <v>10000</v>
+        <v>10001</v>
       </c>
       <c r="B2671" s="0" t="s">
         <v>1828</v>
       </c>
       <c r="D2671" s="0" t="s">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="E2671" s="0" t="s">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="F2671" s="0" t="s">
-        <v>10003</v>
+        <v>10004</v>
       </c>
     </row>
     <row r="2672" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2672" s="0" t="s">
-        <v>10004</v>
+        <v>10005</v>
       </c>
       <c r="B2672" s="0" t="s">
         <v>1828</v>
       </c>
       <c r="D2672" s="0" t="s">
-        <v>10005</v>
+        <v>10006</v>
       </c>
       <c r="E2672" s="0" t="s">
-        <v>10006</v>
+        <v>10007</v>
       </c>
       <c r="F2672" s="0" t="s">
-        <v>10007</v>
+        <v>10008</v>
       </c>
     </row>
     <row r="2673" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2673" s="0" t="s">
-        <v>10008</v>
+        <v>10009</v>
       </c>
       <c r="B2673" s="0" t="s">
         <v>1828</v>
       </c>
       <c r="D2673" s="0" t="s">
-        <v>10009</v>
+        <v>10010</v>
       </c>
       <c r="E2673" s="0" t="s">
-        <v>10010</v>
+        <v>10011</v>
       </c>
       <c r="F2673" s="0" t="s">
-        <v>10011</v>
+        <v>10012</v>
       </c>
     </row>
     <row r="2674" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2674" s="0" t="s">
-        <v>10012</v>
+        <v>10013</v>
       </c>
       <c r="B2674" s="0" t="s">
         <v>1828</v>
       </c>
       <c r="D2674" s="0" t="s">
-        <v>10013</v>
+        <v>10014</v>
       </c>
       <c r="E2674" s="0" t="s">
-        <v>10014</v>
+        <v>10015</v>
       </c>
       <c r="F2674" s="0" t="s">
-        <v>10015</v>
+        <v>10016</v>
       </c>
     </row>
     <row r="2675" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2675" s="0" t="s">
-        <v>10016</v>
+        <v>10017</v>
       </c>
       <c r="B2675" s="0" t="s">
         <v>1828</v>
       </c>
       <c r="D2675" s="0" t="s">
-        <v>10017</v>
+        <v>10018</v>
       </c>
       <c r="E2675" s="0" t="s">
-        <v>10018</v>
+        <v>10019</v>
       </c>
       <c r="F2675" s="0" t="s">
-        <v>10019</v>
-      </c>
-    </row>
-    <row r="2676" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10020</v>
+      </c>
+    </row>
+    <row r="2676" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2676" s="0" t="s">
-        <v>10020</v>
+        <v>10021</v>
       </c>
       <c r="B2676" s="0" t="s">
         <v>1828</v>
       </c>
-      <c r="D2676" s="2" t="s">
-        <v>10021</v>
-      </c>
-      <c r="E2676" s="2" t="s">
+      <c r="D2676" s="0" t="s">
         <v>10022</v>
       </c>
-      <c r="F2676" s="2" t="s">
+      <c r="E2676" s="0" t="s">
         <v>10023</v>
       </c>
-    </row>
-    <row r="2677" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2676" s="0" t="s">
+        <v>10024</v>
+      </c>
+    </row>
+    <row r="2677" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2677" s="0" t="s">
-        <v>10024</v>
+        <v>10025</v>
       </c>
       <c r="B2677" s="0" t="s">
-        <v>4338</v>
-      </c>
-      <c r="D2677" s="0" t="s">
-        <v>10025</v>
-      </c>
-      <c r="E2677" s="0" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D2677" s="2" t="s">
         <v>10026</v>
       </c>
-      <c r="F2677" s="0" t="s">
+      <c r="E2677" s="2" t="s">
         <v>10027</v>
       </c>
-    </row>
-    <row r="2678" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2677" s="2" t="s">
+        <v>10028</v>
+      </c>
+    </row>
+    <row r="2678" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2678" s="0" t="s">
-        <v>10028</v>
+        <v>10029</v>
       </c>
       <c r="B2678" s="0" t="s">
         <v>4338</v>
       </c>
-      <c r="D2678" s="2" t="s">
-        <v>10029</v>
-      </c>
-      <c r="E2678" s="2" t="s">
+      <c r="D2678" s="0" t="s">
         <v>10030</v>
       </c>
-      <c r="F2678" s="2" t="s">
+      <c r="E2678" s="0" t="s">
         <v>10031</v>
       </c>
-    </row>
-    <row r="2679" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2678" s="0" t="s">
+        <v>10032</v>
+      </c>
+    </row>
+    <row r="2679" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2679" s="0" t="s">
-        <v>10032</v>
+        <v>10033</v>
       </c>
       <c r="B2679" s="0" t="s">
-        <v>8362</v>
-      </c>
-      <c r="D2679" s="0" t="s">
-        <v>10033</v>
-      </c>
-      <c r="E2679" s="0" t="s">
+        <v>4338</v>
+      </c>
+      <c r="D2679" s="2" t="s">
         <v>10034</v>
       </c>
-      <c r="F2679" s="0" t="s">
+      <c r="E2679" s="2" t="s">
         <v>10035</v>
       </c>
-    </row>
-    <row r="2680" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2679" s="2" t="s">
+        <v>10036</v>
+      </c>
+    </row>
+    <row r="2680" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2680" s="0" t="s">
-        <v>10036</v>
+        <v>10037</v>
       </c>
       <c r="B2680" s="0" t="s">
         <v>8362</v>
       </c>
-      <c r="D2680" s="2" t="s">
-        <v>10037</v>
-      </c>
-      <c r="E2680" s="2" t="s">
+      <c r="D2680" s="0" t="s">
         <v>10038</v>
       </c>
-      <c r="F2680" s="2" t="s">
+      <c r="E2680" s="0" t="s">
         <v>10039</v>
       </c>
-    </row>
-    <row r="2681" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2680" s="0" t="s">
+        <v>10040</v>
+      </c>
+    </row>
+    <row r="2681" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2681" s="0" t="s">
-        <v>10040</v>
+        <v>10041</v>
       </c>
       <c r="B2681" s="0" t="s">
-        <v>4338</v>
-      </c>
-      <c r="D2681" s="0" t="s">
-        <v>10041</v>
-      </c>
-      <c r="E2681" s="0" t="s">
+        <v>8362</v>
+      </c>
+      <c r="D2681" s="2" t="s">
         <v>10042</v>
       </c>
-      <c r="F2681" s="0" t="s">
+      <c r="E2681" s="2" t="s">
         <v>10043</v>
+      </c>
+      <c r="F2681" s="2" t="s">
+        <v>10044</v>
       </c>
     </row>
     <row r="2682" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2682" s="0" t="s">
-        <v>10044</v>
+        <v>10045</v>
       </c>
       <c r="B2682" s="0" t="s">
-        <v>780</v>
+        <v>4338</v>
       </c>
       <c r="D2682" s="0" t="s">
-        <v>10045</v>
+        <v>10046</v>
       </c>
       <c r="E2682" s="0" t="s">
-        <v>10046</v>
+        <v>10047</v>
       </c>
       <c r="F2682" s="0" t="s">
-        <v>10047</v>
+        <v>10048</v>
       </c>
     </row>
     <row r="2683" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2683" s="0" t="s">
-        <v>10048</v>
+        <v>10049</v>
       </c>
       <c r="B2683" s="0" t="s">
         <v>780</v>
       </c>
       <c r="D2683" s="0" t="s">
-        <v>10049</v>
+        <v>10050</v>
       </c>
       <c r="E2683" s="0" t="s">
-        <v>10050</v>
+        <v>10051</v>
       </c>
       <c r="F2683" s="0" t="s">
-        <v>10051</v>
-      </c>
-    </row>
-    <row r="2684" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10052</v>
+      </c>
+    </row>
+    <row r="2684" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2684" s="0" t="s">
-        <v>10052</v>
+        <v>10053</v>
       </c>
       <c r="B2684" s="0" t="s">
         <v>780</v>
       </c>
-      <c r="D2684" s="2" t="s">
-        <v>10053</v>
-      </c>
-      <c r="E2684" s="2" t="s">
+      <c r="D2684" s="0" t="s">
         <v>10054</v>
       </c>
-      <c r="F2684" s="2" t="s">
+      <c r="E2684" s="0" t="s">
         <v>10055</v>
+      </c>
+      <c r="F2684" s="0" t="s">
+        <v>10056</v>
       </c>
     </row>
     <row r="2685" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2685" s="0" t="s">
-        <v>10056</v>
+        <v>10057</v>
       </c>
       <c r="B2685" s="0" t="s">
+        <v>780</v>
+      </c>
+      <c r="D2685" s="2" t="s">
+        <v>10058</v>
+      </c>
+      <c r="E2685" s="2" t="s">
+        <v>10059</v>
+      </c>
+      <c r="F2685" s="2" t="s">
+        <v>10060</v>
+      </c>
+    </row>
+    <row r="2686" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2686" s="0" t="s">
+        <v>10061</v>
+      </c>
+      <c r="B2686" s="0" t="s">
         <v>8362</v>
       </c>
-      <c r="D2685" s="2" t="s">
-        <v>10057</v>
-      </c>
-      <c r="E2685" s="2" t="s">
-        <v>10058</v>
-      </c>
-      <c r="F2685" s="2" t="s">
-        <v>10059</v>
-      </c>
-    </row>
-    <row r="2686" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2686" s="0" t="s">
-        <v>10060</v>
-      </c>
-      <c r="B2686" s="0" t="s">
-        <v>689</v>
-      </c>
-      <c r="D2686" s="0" t="s">
-        <v>10061</v>
-      </c>
-      <c r="E2686" s="0" t="s">
+      <c r="D2686" s="2" t="s">
         <v>10062</v>
       </c>
-      <c r="F2686" s="0" t="s">
+      <c r="E2686" s="2" t="s">
         <v>10063</v>
+      </c>
+      <c r="F2686" s="2" t="s">
+        <v>10064</v>
       </c>
     </row>
     <row r="2687" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2687" s="0" t="s">
-        <v>10064</v>
+        <v>10065</v>
       </c>
       <c r="B2687" s="0" t="s">
-        <v>1592</v>
+        <v>689</v>
       </c>
       <c r="D2687" s="0" t="s">
-        <v>10065</v>
+        <v>10066</v>
       </c>
       <c r="E2687" s="0" t="s">
-        <v>10066</v>
+        <v>10067</v>
       </c>
       <c r="F2687" s="0" t="s">
-        <v>10067</v>
+        <v>10068</v>
       </c>
     </row>
     <row r="2688" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2688" s="0" t="s">
-        <v>10068</v>
+        <v>10069</v>
       </c>
       <c r="B2688" s="0" t="s">
-        <v>19</v>
+        <v>1592</v>
       </c>
       <c r="D2688" s="0" t="s">
-        <v>10069</v>
+        <v>10070</v>
       </c>
       <c r="E2688" s="0" t="s">
-        <v>10070</v>
+        <v>10071</v>
       </c>
       <c r="F2688" s="0" t="s">
-        <v>10071</v>
+        <v>10072</v>
       </c>
     </row>
     <row r="2689" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2689" s="0" t="s">
-        <v>10072</v>
+        <v>10073</v>
       </c>
       <c r="B2689" s="0" t="s">
-        <v>2960</v>
-      </c>
-      <c r="C2689" s="0" t="s">
-        <v>10073</v>
+        <v>19</v>
       </c>
       <c r="D2689" s="0" t="s">
         <v>10074</v>
@@ -83430,21 +83441,24 @@
         <v>10077</v>
       </c>
       <c r="B2690" s="0" t="s">
-        <v>2876</v>
+        <v>2960</v>
+      </c>
+      <c r="C2690" s="0" t="s">
+        <v>10078</v>
       </c>
       <c r="D2690" s="0" t="s">
-        <v>7960</v>
+        <v>10079</v>
       </c>
       <c r="E2690" s="0" t="s">
-        <v>10078</v>
+        <v>10080</v>
       </c>
       <c r="F2690" s="0" t="s">
-        <v>7962</v>
+        <v>10081</v>
       </c>
     </row>
     <row r="2691" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2691" s="0" t="s">
-        <v>10079</v>
+        <v>10082</v>
       </c>
       <c r="B2691" s="0" t="s">
         <v>2876</v>
@@ -83453,7 +83467,7 @@
         <v>7960</v>
       </c>
       <c r="E2691" s="0" t="s">
-        <v>10078</v>
+        <v>10083</v>
       </c>
       <c r="F2691" s="0" t="s">
         <v>7962</v>
@@ -83461,1773 +83475,1790 @@
     </row>
     <row r="2692" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2692" s="0" t="s">
-        <v>10080</v>
+        <v>10084</v>
       </c>
       <c r="B2692" s="0" t="s">
         <v>2876</v>
       </c>
       <c r="D2692" s="0" t="s">
-        <v>10081</v>
+        <v>7960</v>
       </c>
       <c r="E2692" s="0" t="s">
-        <v>10082</v>
+        <v>10083</v>
       </c>
       <c r="F2692" s="0" t="s">
-        <v>10083</v>
+        <v>7962</v>
       </c>
     </row>
     <row r="2693" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2693" s="0" t="s">
-        <v>10084</v>
+        <v>10085</v>
       </c>
       <c r="B2693" s="0" t="s">
         <v>2876</v>
       </c>
       <c r="D2693" s="0" t="s">
-        <v>10085</v>
+        <v>10086</v>
       </c>
       <c r="E2693" s="0" t="s">
-        <v>10086</v>
+        <v>10087</v>
       </c>
       <c r="F2693" s="0" t="s">
-        <v>10087</v>
+        <v>10088</v>
       </c>
     </row>
     <row r="2694" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2694" s="0" t="s">
-        <v>10088</v>
+        <v>10089</v>
       </c>
       <c r="B2694" s="0" t="s">
         <v>2876</v>
       </c>
       <c r="D2694" s="0" t="s">
-        <v>10089</v>
+        <v>10090</v>
       </c>
       <c r="E2694" s="0" t="s">
-        <v>10090</v>
+        <v>10091</v>
       </c>
       <c r="F2694" s="0" t="s">
-        <v>10091</v>
+        <v>10092</v>
       </c>
     </row>
     <row r="2695" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2695" s="0" t="s">
-        <v>10092</v>
+        <v>10093</v>
       </c>
       <c r="B2695" s="0" t="s">
         <v>2876</v>
       </c>
       <c r="D2695" s="0" t="s">
-        <v>10093</v>
+        <v>10094</v>
       </c>
       <c r="E2695" s="0" t="s">
-        <v>10094</v>
+        <v>10095</v>
       </c>
       <c r="F2695" s="0" t="s">
-        <v>10095</v>
+        <v>10096</v>
       </c>
     </row>
     <row r="2696" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2696" s="0" t="s">
-        <v>10096</v>
+        <v>10097</v>
       </c>
       <c r="B2696" s="0" t="s">
         <v>2876</v>
       </c>
       <c r="D2696" s="0" t="s">
-        <v>10097</v>
+        <v>10098</v>
       </c>
       <c r="E2696" s="0" t="s">
-        <v>10098</v>
+        <v>10099</v>
       </c>
       <c r="F2696" s="0" t="s">
-        <v>10099</v>
+        <v>10100</v>
       </c>
     </row>
     <row r="2697" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2697" s="0" t="s">
-        <v>10100</v>
+        <v>10101</v>
       </c>
       <c r="B2697" s="0" t="s">
         <v>2876</v>
       </c>
       <c r="D2697" s="0" t="s">
-        <v>10101</v>
+        <v>10102</v>
       </c>
       <c r="E2697" s="0" t="s">
-        <v>10102</v>
+        <v>10103</v>
       </c>
       <c r="F2697" s="0" t="s">
-        <v>10103</v>
+        <v>10104</v>
       </c>
     </row>
     <row r="2698" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2698" s="0" t="s">
-        <v>10104</v>
+        <v>10105</v>
       </c>
       <c r="B2698" s="0" t="s">
         <v>2876</v>
       </c>
       <c r="D2698" s="0" t="s">
-        <v>10105</v>
+        <v>10106</v>
       </c>
       <c r="E2698" s="0" t="s">
-        <v>10106</v>
+        <v>10107</v>
       </c>
       <c r="F2698" s="0" t="s">
-        <v>10107</v>
+        <v>10108</v>
       </c>
     </row>
     <row r="2699" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2699" s="0" t="s">
-        <v>10108</v>
+        <v>10109</v>
       </c>
       <c r="B2699" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2699" s="0" t="s">
-        <v>8573</v>
+        <v>2876</v>
       </c>
       <c r="D2699" s="0" t="s">
-        <v>10109</v>
+        <v>10110</v>
       </c>
       <c r="E2699" s="0" t="s">
-        <v>10110</v>
+        <v>10111</v>
       </c>
       <c r="F2699" s="0" t="s">
-        <v>10111</v>
+        <v>10112</v>
       </c>
     </row>
     <row r="2700" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2700" s="0" t="s">
-        <v>10112</v>
+        <v>10113</v>
       </c>
       <c r="B2700" s="0" t="s">
         <v>45</v>
       </c>
+      <c r="C2700" s="0" t="s">
+        <v>8573</v>
+      </c>
       <c r="D2700" s="0" t="s">
-        <v>10113</v>
+        <v>10114</v>
       </c>
       <c r="E2700" s="0" t="s">
-        <v>10114</v>
+        <v>10115</v>
       </c>
       <c r="F2700" s="0" t="s">
-        <v>10115</v>
+        <v>10116</v>
       </c>
     </row>
     <row r="2701" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2701" s="0" t="s">
-        <v>10116</v>
+        <v>10117</v>
       </c>
       <c r="B2701" s="0" t="s">
-        <v>364</v>
+        <v>45</v>
       </c>
       <c r="D2701" s="0" t="s">
-        <v>10117</v>
+        <v>10118</v>
       </c>
       <c r="E2701" s="0" t="s">
-        <v>10118</v>
+        <v>10119</v>
       </c>
       <c r="F2701" s="0" t="s">
-        <v>10119</v>
+        <v>10120</v>
       </c>
     </row>
     <row r="2702" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2702" s="0" t="s">
-        <v>10120</v>
+        <v>10121</v>
       </c>
       <c r="B2702" s="0" t="s">
-        <v>45</v>
+        <v>364</v>
       </c>
       <c r="D2702" s="0" t="s">
-        <v>10121</v>
+        <v>10122</v>
       </c>
       <c r="E2702" s="0" t="s">
-        <v>10122</v>
+        <v>10123</v>
       </c>
       <c r="F2702" s="0" t="s">
-        <v>10123</v>
+        <v>10124</v>
       </c>
     </row>
     <row r="2703" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2703" s="0" t="s">
-        <v>10124</v>
+        <v>10125</v>
       </c>
       <c r="B2703" s="0" t="s">
-        <v>364</v>
+        <v>45</v>
       </c>
       <c r="D2703" s="0" t="s">
-        <v>8777</v>
+        <v>10126</v>
       </c>
       <c r="E2703" s="0" t="s">
-        <v>8778</v>
+        <v>10127</v>
       </c>
       <c r="F2703" s="0" t="s">
-        <v>8779</v>
+        <v>10128</v>
       </c>
     </row>
     <row r="2704" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2704" s="0" t="s">
-        <v>10125</v>
+        <v>10129</v>
       </c>
       <c r="B2704" s="0" t="s">
         <v>364</v>
       </c>
       <c r="D2704" s="0" t="s">
-        <v>10126</v>
+        <v>8777</v>
       </c>
       <c r="E2704" s="0" t="s">
-        <v>10127</v>
+        <v>8778</v>
       </c>
       <c r="F2704" s="0" t="s">
-        <v>10128</v>
+        <v>8779</v>
       </c>
     </row>
     <row r="2705" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2705" s="0" t="s">
-        <v>10129</v>
+        <v>10130</v>
       </c>
       <c r="B2705" s="0" t="s">
         <v>364</v>
       </c>
       <c r="D2705" s="0" t="s">
-        <v>10130</v>
+        <v>10131</v>
       </c>
       <c r="E2705" s="0" t="s">
-        <v>10131</v>
+        <v>10132</v>
       </c>
       <c r="F2705" s="0" t="s">
-        <v>10132</v>
+        <v>10133</v>
       </c>
     </row>
     <row r="2706" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2706" s="0" t="s">
-        <v>10133</v>
+        <v>10134</v>
       </c>
       <c r="B2706" s="0" t="s">
         <v>364</v>
       </c>
       <c r="D2706" s="0" t="s">
-        <v>10134</v>
+        <v>10135</v>
       </c>
       <c r="E2706" s="0" t="s">
-        <v>10135</v>
+        <v>10136</v>
       </c>
       <c r="F2706" s="0" t="s">
-        <v>10136</v>
+        <v>10137</v>
       </c>
     </row>
     <row r="2707" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2707" s="0" t="s">
-        <v>10137</v>
+        <v>10138</v>
       </c>
       <c r="B2707" s="0" t="s">
         <v>364</v>
       </c>
       <c r="D2707" s="0" t="s">
-        <v>10138</v>
+        <v>10139</v>
       </c>
       <c r="E2707" s="0" t="s">
-        <v>10139</v>
+        <v>10140</v>
       </c>
       <c r="F2707" s="0" t="s">
-        <v>10140</v>
+        <v>10141</v>
       </c>
     </row>
     <row r="2708" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2708" s="0" t="s">
-        <v>10141</v>
+        <v>10142</v>
       </c>
       <c r="B2708" s="0" t="s">
         <v>364</v>
       </c>
       <c r="D2708" s="0" t="s">
-        <v>10142</v>
+        <v>10143</v>
       </c>
       <c r="E2708" s="0" t="s">
-        <v>10143</v>
+        <v>10144</v>
       </c>
       <c r="F2708" s="0" t="s">
-        <v>10144</v>
+        <v>10145</v>
       </c>
     </row>
     <row r="2709" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2709" s="0" t="s">
-        <v>10145</v>
+        <v>10146</v>
       </c>
       <c r="B2709" s="0" t="s">
         <v>364</v>
       </c>
       <c r="D2709" s="0" t="s">
-        <v>10146</v>
+        <v>10147</v>
       </c>
       <c r="E2709" s="0" t="s">
-        <v>10147</v>
+        <v>10148</v>
       </c>
       <c r="F2709" s="0" t="s">
-        <v>10148</v>
+        <v>10149</v>
       </c>
     </row>
     <row r="2710" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2710" s="0" t="s">
-        <v>10149</v>
+        <v>10150</v>
       </c>
       <c r="B2710" s="0" t="s">
-        <v>3054</v>
+        <v>364</v>
       </c>
       <c r="D2710" s="0" t="s">
-        <v>10150</v>
+        <v>10151</v>
       </c>
       <c r="E2710" s="0" t="s">
-        <v>10151</v>
+        <v>10152</v>
       </c>
       <c r="F2710" s="0" t="s">
-        <v>10152</v>
+        <v>10153</v>
       </c>
     </row>
     <row r="2711" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2711" s="0" t="s">
-        <v>10153</v>
+        <v>10154</v>
       </c>
       <c r="B2711" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2711" s="0" t="s">
-        <v>10154</v>
+        <v>10155</v>
       </c>
       <c r="E2711" s="0" t="s">
-        <v>10155</v>
+        <v>10156</v>
       </c>
       <c r="F2711" s="0" t="s">
-        <v>10156</v>
+        <v>10157</v>
       </c>
     </row>
     <row r="2712" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2712" s="0" t="s">
-        <v>10157</v>
+        <v>10158</v>
       </c>
       <c r="B2712" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2712" s="0" t="s">
-        <v>10158</v>
+        <v>10159</v>
       </c>
       <c r="E2712" s="0" t="s">
-        <v>10159</v>
+        <v>10160</v>
       </c>
       <c r="F2712" s="0" t="s">
-        <v>10160</v>
+        <v>10161</v>
       </c>
     </row>
     <row r="2713" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2713" s="0" t="s">
-        <v>10161</v>
+        <v>10162</v>
       </c>
       <c r="B2713" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2713" s="0" t="s">
-        <v>10162</v>
+        <v>10163</v>
       </c>
       <c r="E2713" s="0" t="s">
-        <v>10163</v>
+        <v>10164</v>
       </c>
       <c r="F2713" s="0" t="s">
-        <v>10164</v>
+        <v>10165</v>
       </c>
     </row>
     <row r="2714" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2714" s="0" t="s">
-        <v>10165</v>
+        <v>10166</v>
       </c>
       <c r="B2714" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2714" s="0" t="s">
-        <v>10166</v>
+        <v>10167</v>
       </c>
       <c r="E2714" s="0" t="s">
-        <v>10167</v>
+        <v>10168</v>
       </c>
       <c r="F2714" s="0" t="s">
-        <v>10168</v>
-      </c>
-    </row>
-    <row r="2715" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10169</v>
+      </c>
+    </row>
+    <row r="2715" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2715" s="0" t="s">
-        <v>10169</v>
+        <v>10170</v>
       </c>
       <c r="B2715" s="0" t="s">
         <v>3054</v>
       </c>
-      <c r="D2715" s="2" t="s">
-        <v>10170</v>
-      </c>
-      <c r="E2715" s="2" t="s">
+      <c r="D2715" s="0" t="s">
         <v>10171</v>
       </c>
-      <c r="F2715" s="2" t="s">
+      <c r="E2715" s="0" t="s">
         <v>10172</v>
       </c>
-    </row>
-    <row r="2716" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2715" s="0" t="s">
+        <v>10173</v>
+      </c>
+    </row>
+    <row r="2716" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2716" s="0" t="s">
-        <v>10173</v>
+        <v>10174</v>
       </c>
       <c r="B2716" s="0" t="s">
         <v>3054</v>
       </c>
-      <c r="D2716" s="0" t="s">
-        <v>10174</v>
-      </c>
-      <c r="E2716" s="0" t="s">
+      <c r="D2716" s="2" t="s">
         <v>10175</v>
       </c>
-      <c r="F2716" s="0" t="s">
+      <c r="E2716" s="2" t="s">
         <v>10176</v>
+      </c>
+      <c r="F2716" s="2" t="s">
+        <v>10177</v>
       </c>
     </row>
     <row r="2717" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2717" s="0" t="s">
-        <v>10177</v>
+        <v>10178</v>
       </c>
       <c r="B2717" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2717" s="0" t="s">
-        <v>10178</v>
+        <v>10179</v>
       </c>
       <c r="E2717" s="0" t="s">
-        <v>10179</v>
+        <v>10180</v>
       </c>
       <c r="F2717" s="0" t="s">
-        <v>10180</v>
-      </c>
-    </row>
-    <row r="2718" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10181</v>
+      </c>
+    </row>
+    <row r="2718" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2718" s="0" t="s">
-        <v>10181</v>
+        <v>10182</v>
       </c>
       <c r="B2718" s="0" t="s">
         <v>3054</v>
       </c>
-      <c r="D2718" s="2" t="s">
-        <v>10182</v>
-      </c>
-      <c r="E2718" s="2" t="s">
+      <c r="D2718" s="0" t="s">
         <v>10183</v>
       </c>
-      <c r="F2718" s="2" t="s">
+      <c r="E2718" s="0" t="s">
         <v>10184</v>
       </c>
-    </row>
-    <row r="2719" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2718" s="0" t="s">
+        <v>10185</v>
+      </c>
+    </row>
+    <row r="2719" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2719" s="0" t="s">
-        <v>10185</v>
+        <v>10186</v>
       </c>
       <c r="B2719" s="0" t="s">
         <v>3054</v>
       </c>
-      <c r="D2719" s="0" t="s">
-        <v>10186</v>
-      </c>
-      <c r="E2719" s="0" t="s">
+      <c r="D2719" s="2" t="s">
         <v>10187</v>
       </c>
-      <c r="F2719" s="0" t="s">
+      <c r="E2719" s="2" t="s">
         <v>10188</v>
       </c>
-    </row>
-    <row r="2720" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2719" s="2" t="s">
+        <v>10189</v>
+      </c>
+    </row>
+    <row r="2720" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2720" s="0" t="s">
-        <v>10189</v>
+        <v>10190</v>
       </c>
       <c r="B2720" s="0" t="s">
         <v>3054</v>
       </c>
-      <c r="D2720" s="2" t="s">
-        <v>10190</v>
-      </c>
-      <c r="E2720" s="2" t="s">
+      <c r="D2720" s="0" t="s">
         <v>10191</v>
       </c>
-      <c r="F2720" s="2" t="s">
+      <c r="E2720" s="0" t="s">
         <v>10192</v>
       </c>
-    </row>
-    <row r="2721" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2720" s="0" t="s">
+        <v>10193</v>
+      </c>
+    </row>
+    <row r="2721" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2721" s="0" t="s">
-        <v>10193</v>
+        <v>10194</v>
       </c>
       <c r="B2721" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2721" s="2" t="s">
-        <v>10194</v>
+        <v>10195</v>
       </c>
       <c r="E2721" s="2" t="s">
-        <v>10195</v>
+        <v>10196</v>
       </c>
       <c r="F2721" s="2" t="s">
-        <v>10196</v>
-      </c>
-    </row>
-    <row r="2722" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10197</v>
+      </c>
+    </row>
+    <row r="2722" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2722" s="0" t="s">
-        <v>10197</v>
+        <v>10198</v>
       </c>
       <c r="B2722" s="0" t="s">
         <v>3054</v>
       </c>
-      <c r="D2722" s="0" t="s">
-        <v>10198</v>
-      </c>
-      <c r="E2722" s="0" t="s">
+      <c r="D2722" s="2" t="s">
         <v>10199</v>
       </c>
-      <c r="F2722" s="0" t="s">
+      <c r="E2722" s="2" t="s">
         <v>10200</v>
       </c>
-    </row>
-    <row r="2723" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2722" s="2" t="s">
+        <v>10201</v>
+      </c>
+    </row>
+    <row r="2723" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2723" s="0" t="s">
-        <v>10201</v>
+        <v>10202</v>
       </c>
       <c r="B2723" s="0" t="s">
         <v>3054</v>
       </c>
-      <c r="D2723" s="2" t="s">
-        <v>10202</v>
-      </c>
-      <c r="E2723" s="2" t="s">
+      <c r="D2723" s="0" t="s">
         <v>10203</v>
       </c>
-      <c r="F2723" s="2" t="s">
+      <c r="E2723" s="0" t="s">
         <v>10204</v>
       </c>
-    </row>
-    <row r="2724" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2723" s="0" t="s">
+        <v>10205</v>
+      </c>
+    </row>
+    <row r="2724" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2724" s="0" t="s">
-        <v>10205</v>
+        <v>10206</v>
       </c>
       <c r="B2724" s="0" t="s">
         <v>3054</v>
       </c>
-      <c r="D2724" s="0" t="s">
-        <v>10206</v>
-      </c>
-      <c r="E2724" s="0" t="s">
+      <c r="D2724" s="2" t="s">
         <v>10207</v>
       </c>
-      <c r="F2724" s="0" t="s">
+      <c r="E2724" s="2" t="s">
         <v>10208</v>
+      </c>
+      <c r="F2724" s="2" t="s">
+        <v>10209</v>
       </c>
     </row>
     <row r="2725" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2725" s="0" t="s">
-        <v>10209</v>
+        <v>10210</v>
       </c>
       <c r="B2725" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2725" s="0" t="s">
-        <v>10210</v>
+        <v>10211</v>
       </c>
       <c r="E2725" s="0" t="s">
-        <v>10211</v>
+        <v>10212</v>
       </c>
       <c r="F2725" s="0" t="s">
-        <v>10212</v>
+        <v>10213</v>
       </c>
     </row>
     <row r="2726" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2726" s="0" t="s">
-        <v>10213</v>
+        <v>10214</v>
       </c>
       <c r="B2726" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2726" s="0" t="s">
-        <v>10214</v>
+        <v>10215</v>
       </c>
       <c r="E2726" s="0" t="s">
-        <v>10215</v>
+        <v>10216</v>
       </c>
       <c r="F2726" s="0" t="s">
-        <v>10216</v>
+        <v>10217</v>
       </c>
     </row>
     <row r="2727" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2727" s="0" t="s">
-        <v>10217</v>
+        <v>10218</v>
       </c>
       <c r="B2727" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2727" s="0" t="s">
-        <v>10218</v>
+        <v>10219</v>
       </c>
       <c r="E2727" s="0" t="s">
-        <v>10219</v>
+        <v>10220</v>
       </c>
       <c r="F2727" s="0" t="s">
-        <v>10220</v>
-      </c>
-    </row>
-    <row r="2728" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10221</v>
+      </c>
+    </row>
+    <row r="2728" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2728" s="0" t="s">
-        <v>10221</v>
+        <v>10222</v>
       </c>
       <c r="B2728" s="0" t="s">
         <v>3054</v>
       </c>
-      <c r="D2728" s="2" t="s">
-        <v>10222</v>
-      </c>
-      <c r="E2728" s="2" t="s">
+      <c r="D2728" s="0" t="s">
         <v>10223</v>
       </c>
-      <c r="F2728" s="2" t="s">
+      <c r="E2728" s="0" t="s">
         <v>10224</v>
       </c>
-    </row>
-    <row r="2729" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2728" s="0" t="s">
+        <v>10225</v>
+      </c>
+    </row>
+    <row r="2729" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2729" s="0" t="s">
-        <v>10225</v>
+        <v>10226</v>
       </c>
       <c r="B2729" s="0" t="s">
         <v>3054</v>
       </c>
-      <c r="D2729" s="0" t="s">
-        <v>10226</v>
-      </c>
-      <c r="E2729" s="0" t="s">
+      <c r="D2729" s="2" t="s">
         <v>10227</v>
       </c>
-      <c r="F2729" s="0" t="s">
+      <c r="E2729" s="2" t="s">
         <v>10228</v>
+      </c>
+      <c r="F2729" s="2" t="s">
+        <v>10229</v>
       </c>
     </row>
     <row r="2730" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2730" s="0" t="s">
-        <v>10229</v>
+        <v>10230</v>
       </c>
       <c r="B2730" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2730" s="0" t="s">
-        <v>10230</v>
+        <v>10231</v>
       </c>
       <c r="E2730" s="0" t="s">
-        <v>10231</v>
+        <v>10232</v>
       </c>
       <c r="F2730" s="0" t="s">
-        <v>10232</v>
+        <v>10233</v>
       </c>
     </row>
     <row r="2731" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2731" s="0" t="s">
-        <v>10233</v>
+        <v>10234</v>
       </c>
       <c r="B2731" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2731" s="0" t="s">
-        <v>10234</v>
+        <v>10235</v>
       </c>
       <c r="E2731" s="0" t="s">
-        <v>10235</v>
+        <v>10236</v>
       </c>
       <c r="F2731" s="0" t="s">
-        <v>10236</v>
-      </c>
-    </row>
-    <row r="2732" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10237</v>
+      </c>
+    </row>
+    <row r="2732" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2732" s="0" t="s">
-        <v>10237</v>
+        <v>10238</v>
       </c>
       <c r="B2732" s="0" t="s">
         <v>3054</v>
       </c>
-      <c r="D2732" s="2" t="s">
-        <v>10238</v>
-      </c>
-      <c r="E2732" s="2" t="s">
+      <c r="D2732" s="0" t="s">
         <v>10239</v>
       </c>
-      <c r="F2732" s="2" t="s">
+      <c r="E2732" s="0" t="s">
         <v>10240</v>
       </c>
-    </row>
-    <row r="2733" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2732" s="0" t="s">
+        <v>10241</v>
+      </c>
+    </row>
+    <row r="2733" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2733" s="0" t="s">
-        <v>10241</v>
+        <v>10242</v>
       </c>
       <c r="B2733" s="0" t="s">
         <v>3054</v>
       </c>
-      <c r="D2733" s="0" t="s">
-        <v>10242</v>
-      </c>
-      <c r="E2733" s="0" t="s">
+      <c r="D2733" s="2" t="s">
         <v>10243</v>
       </c>
-      <c r="F2733" s="0" t="s">
+      <c r="E2733" s="2" t="s">
         <v>10244</v>
       </c>
-    </row>
-    <row r="2734" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2733" s="2" t="s">
+        <v>10245</v>
+      </c>
+    </row>
+    <row r="2734" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2734" s="0" t="s">
-        <v>10245</v>
+        <v>10246</v>
       </c>
       <c r="B2734" s="0" t="s">
         <v>3054</v>
       </c>
-      <c r="D2734" s="2" t="s">
-        <v>10246</v>
-      </c>
-      <c r="E2734" s="2" t="s">
+      <c r="D2734" s="0" t="s">
         <v>10247</v>
       </c>
-      <c r="F2734" s="2" t="s">
+      <c r="E2734" s="0" t="s">
         <v>10248</v>
       </c>
-    </row>
-    <row r="2735" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2734" s="0" t="s">
+        <v>10249</v>
+      </c>
+    </row>
+    <row r="2735" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2735" s="0" t="s">
-        <v>10249</v>
+        <v>10250</v>
       </c>
       <c r="B2735" s="0" t="s">
         <v>3054</v>
       </c>
-      <c r="D2735" s="0" t="s">
-        <v>10250</v>
-      </c>
-      <c r="E2735" s="0" t="s">
+      <c r="D2735" s="2" t="s">
         <v>10251</v>
       </c>
-      <c r="F2735" s="0" t="s">
+      <c r="E2735" s="2" t="s">
         <v>10252</v>
+      </c>
+      <c r="F2735" s="2" t="s">
+        <v>10253</v>
       </c>
     </row>
     <row r="2736" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2736" s="0" t="s">
-        <v>10253</v>
+        <v>10254</v>
       </c>
       <c r="B2736" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2736" s="0" t="s">
-        <v>10254</v>
+        <v>10255</v>
       </c>
       <c r="E2736" s="0" t="s">
-        <v>10255</v>
+        <v>10256</v>
       </c>
       <c r="F2736" s="0" t="s">
-        <v>10256</v>
+        <v>10257</v>
       </c>
     </row>
     <row r="2737" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2737" s="0" t="s">
-        <v>10257</v>
+        <v>10258</v>
       </c>
       <c r="B2737" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2737" s="0" t="s">
-        <v>10258</v>
+        <v>10259</v>
       </c>
       <c r="E2737" s="0" t="s">
-        <v>10259</v>
+        <v>10260</v>
       </c>
       <c r="F2737" s="0" t="s">
-        <v>5989</v>
+        <v>10261</v>
       </c>
     </row>
     <row r="2738" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2738" s="0" t="s">
-        <v>10260</v>
+        <v>10262</v>
       </c>
       <c r="B2738" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2738" s="0" t="s">
-        <v>10261</v>
+        <v>10263</v>
       </c>
       <c r="E2738" s="0" t="s">
-        <v>10262</v>
+        <v>10264</v>
       </c>
       <c r="F2738" s="0" t="s">
-        <v>10263</v>
+        <v>5989</v>
       </c>
     </row>
     <row r="2739" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2739" s="0" t="s">
-        <v>10264</v>
+        <v>10265</v>
       </c>
       <c r="B2739" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2739" s="0" t="s">
-        <v>10265</v>
+        <v>10266</v>
       </c>
       <c r="E2739" s="0" t="s">
-        <v>10266</v>
+        <v>10267</v>
       </c>
       <c r="F2739" s="0" t="s">
-        <v>10267</v>
+        <v>10268</v>
       </c>
     </row>
     <row r="2740" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2740" s="0" t="s">
-        <v>10268</v>
+        <v>10269</v>
       </c>
       <c r="B2740" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2740" s="0" t="s">
-        <v>10269</v>
+        <v>10270</v>
       </c>
       <c r="E2740" s="0" t="s">
-        <v>10270</v>
+        <v>10271</v>
       </c>
       <c r="F2740" s="0" t="s">
-        <v>10271</v>
+        <v>10272</v>
       </c>
     </row>
     <row r="2741" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2741" s="0" t="s">
-        <v>10272</v>
+        <v>10273</v>
       </c>
       <c r="B2741" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2741" s="0" t="s">
-        <v>10273</v>
+        <v>10274</v>
       </c>
       <c r="E2741" s="0" t="s">
-        <v>10274</v>
+        <v>10275</v>
       </c>
       <c r="F2741" s="0" t="s">
-        <v>10275</v>
+        <v>10276</v>
       </c>
     </row>
     <row r="2742" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2742" s="0" t="s">
-        <v>10276</v>
+        <v>10277</v>
       </c>
       <c r="B2742" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2742" s="0" t="s">
-        <v>10277</v>
+        <v>10278</v>
       </c>
       <c r="E2742" s="0" t="s">
-        <v>10278</v>
+        <v>10279</v>
       </c>
       <c r="F2742" s="0" t="s">
-        <v>10279</v>
+        <v>10280</v>
       </c>
     </row>
     <row r="2743" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2743" s="0" t="s">
-        <v>10280</v>
+        <v>10281</v>
       </c>
       <c r="B2743" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2743" s="0" t="s">
-        <v>10281</v>
+        <v>10282</v>
       </c>
       <c r="E2743" s="0" t="s">
-        <v>10282</v>
+        <v>10283</v>
       </c>
       <c r="F2743" s="0" t="s">
-        <v>10283</v>
+        <v>10284</v>
       </c>
     </row>
     <row r="2744" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2744" s="0" t="s">
-        <v>10284</v>
+        <v>10285</v>
       </c>
       <c r="B2744" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2744" s="0" t="s">
-        <v>10285</v>
+        <v>10286</v>
       </c>
       <c r="E2744" s="0" t="s">
-        <v>10286</v>
+        <v>10287</v>
       </c>
       <c r="F2744" s="0" t="s">
-        <v>10287</v>
+        <v>10288</v>
       </c>
     </row>
     <row r="2745" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2745" s="0" t="s">
-        <v>10288</v>
+        <v>10289</v>
       </c>
       <c r="B2745" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2745" s="0" t="s">
-        <v>10289</v>
+        <v>10290</v>
       </c>
       <c r="E2745" s="0" t="s">
-        <v>10290</v>
+        <v>10291</v>
       </c>
       <c r="F2745" s="0" t="s">
-        <v>10291</v>
+        <v>10292</v>
       </c>
     </row>
     <row r="2746" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2746" s="0" t="s">
-        <v>10292</v>
+        <v>10293</v>
       </c>
       <c r="B2746" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2746" s="0" t="s">
-        <v>10293</v>
+        <v>10294</v>
       </c>
       <c r="E2746" s="0" t="s">
-        <v>10294</v>
+        <v>10295</v>
       </c>
       <c r="F2746" s="0" t="s">
-        <v>10295</v>
+        <v>10296</v>
       </c>
     </row>
     <row r="2747" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2747" s="0" t="s">
-        <v>10296</v>
+        <v>10297</v>
       </c>
       <c r="B2747" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2747" s="0" t="s">
-        <v>10297</v>
+        <v>10298</v>
       </c>
       <c r="E2747" s="0" t="s">
-        <v>10298</v>
+        <v>10299</v>
       </c>
       <c r="F2747" s="0" t="s">
-        <v>10299</v>
+        <v>10300</v>
       </c>
     </row>
     <row r="2748" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2748" s="0" t="s">
-        <v>10300</v>
+        <v>10301</v>
       </c>
       <c r="B2748" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2748" s="0" t="s">
-        <v>10301</v>
+        <v>10302</v>
       </c>
       <c r="E2748" s="0" t="s">
-        <v>10302</v>
+        <v>10303</v>
       </c>
       <c r="F2748" s="0" t="s">
-        <v>10303</v>
+        <v>10304</v>
       </c>
     </row>
     <row r="2749" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2749" s="0" t="s">
-        <v>10304</v>
+        <v>10305</v>
       </c>
       <c r="B2749" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2749" s="0" t="s">
-        <v>10305</v>
+        <v>10306</v>
       </c>
       <c r="E2749" s="0" t="s">
-        <v>10306</v>
+        <v>10307</v>
       </c>
       <c r="F2749" s="0" t="s">
-        <v>10307</v>
+        <v>10308</v>
       </c>
     </row>
     <row r="2750" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2750" s="0" t="s">
-        <v>10308</v>
+        <v>10309</v>
       </c>
       <c r="B2750" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2750" s="0" t="s">
-        <v>10309</v>
+        <v>10310</v>
       </c>
       <c r="E2750" s="0" t="s">
-        <v>10310</v>
+        <v>10311</v>
       </c>
       <c r="F2750" s="0" t="s">
-        <v>10311</v>
+        <v>10312</v>
       </c>
     </row>
     <row r="2751" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2751" s="0" t="s">
-        <v>10312</v>
+        <v>10313</v>
       </c>
       <c r="B2751" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2751" s="0" t="s">
-        <v>10313</v>
+        <v>10314</v>
       </c>
       <c r="E2751" s="0" t="s">
-        <v>10314</v>
+        <v>10315</v>
       </c>
       <c r="F2751" s="0" t="s">
-        <v>10315</v>
+        <v>10316</v>
       </c>
     </row>
     <row r="2752" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2752" s="0" t="s">
-        <v>10316</v>
+        <v>10317</v>
       </c>
       <c r="B2752" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2752" s="0" t="s">
-        <v>10317</v>
+        <v>10318</v>
       </c>
       <c r="E2752" s="0" t="s">
-        <v>10318</v>
+        <v>10319</v>
       </c>
       <c r="F2752" s="0" t="s">
-        <v>10319</v>
+        <v>10320</v>
       </c>
     </row>
     <row r="2753" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2753" s="0" t="s">
-        <v>10320</v>
+        <v>10321</v>
       </c>
       <c r="B2753" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2753" s="0" t="s">
-        <v>10321</v>
+        <v>10322</v>
       </c>
       <c r="E2753" s="0" t="s">
-        <v>10322</v>
+        <v>10323</v>
       </c>
       <c r="F2753" s="0" t="s">
-        <v>10323</v>
+        <v>10324</v>
       </c>
     </row>
     <row r="2754" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2754" s="0" t="s">
-        <v>10324</v>
+        <v>10325</v>
       </c>
       <c r="B2754" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2754" s="0" t="s">
-        <v>10325</v>
+        <v>10326</v>
       </c>
       <c r="E2754" s="0" t="s">
-        <v>10326</v>
+        <v>10327</v>
       </c>
       <c r="F2754" s="0" t="s">
-        <v>10327</v>
+        <v>10328</v>
       </c>
     </row>
     <row r="2755" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2755" s="0" t="s">
-        <v>10328</v>
+        <v>10329</v>
       </c>
       <c r="B2755" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2755" s="0" t="s">
-        <v>10329</v>
+        <v>10330</v>
       </c>
       <c r="E2755" s="0" t="s">
-        <v>10330</v>
+        <v>10331</v>
       </c>
       <c r="F2755" s="0" t="s">
-        <v>10331</v>
+        <v>10332</v>
       </c>
     </row>
     <row r="2756" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2756" s="0" t="s">
-        <v>10332</v>
+        <v>10333</v>
       </c>
       <c r="B2756" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2756" s="0" t="s">
-        <v>10333</v>
+        <v>10334</v>
       </c>
       <c r="E2756" s="0" t="s">
-        <v>10334</v>
+        <v>10335</v>
       </c>
       <c r="F2756" s="0" t="s">
-        <v>10335</v>
+        <v>10336</v>
       </c>
     </row>
     <row r="2757" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2757" s="0" t="s">
-        <v>10336</v>
+        <v>10337</v>
       </c>
       <c r="B2757" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2757" s="0" t="s">
-        <v>10337</v>
+        <v>10338</v>
       </c>
       <c r="E2757" s="0" t="s">
-        <v>10338</v>
+        <v>10339</v>
       </c>
       <c r="F2757" s="0" t="s">
-        <v>10339</v>
+        <v>10340</v>
       </c>
     </row>
     <row r="2758" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2758" s="0" t="s">
-        <v>10340</v>
+        <v>10341</v>
       </c>
       <c r="B2758" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2758" s="0" t="s">
-        <v>10341</v>
+        <v>10342</v>
       </c>
       <c r="E2758" s="0" t="s">
-        <v>10342</v>
+        <v>10343</v>
       </c>
       <c r="F2758" s="0" t="s">
-        <v>10343</v>
-      </c>
-    </row>
-    <row r="2759" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10344</v>
+      </c>
+    </row>
+    <row r="2759" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2759" s="0" t="s">
-        <v>10344</v>
+        <v>10345</v>
       </c>
       <c r="B2759" s="0" t="s">
         <v>3054</v>
       </c>
-      <c r="D2759" s="2" t="s">
-        <v>10345</v>
-      </c>
-      <c r="E2759" s="2" t="s">
+      <c r="D2759" s="0" t="s">
         <v>10346</v>
       </c>
-      <c r="F2759" s="2" t="s">
+      <c r="E2759" s="0" t="s">
         <v>10347</v>
       </c>
-    </row>
-    <row r="2760" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2759" s="0" t="s">
+        <v>10348</v>
+      </c>
+    </row>
+    <row r="2760" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2760" s="0" t="s">
-        <v>10348</v>
+        <v>10349</v>
       </c>
       <c r="B2760" s="0" t="s">
         <v>3054</v>
       </c>
-      <c r="D2760" s="0" t="s">
-        <v>10349</v>
-      </c>
-      <c r="E2760" s="0" t="s">
+      <c r="D2760" s="2" t="s">
         <v>10350</v>
       </c>
-      <c r="F2760" s="0" t="s">
+      <c r="E2760" s="2" t="s">
         <v>10351</v>
+      </c>
+      <c r="F2760" s="2" t="s">
+        <v>10352</v>
       </c>
     </row>
     <row r="2761" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2761" s="0" t="s">
-        <v>10352</v>
+        <v>10353</v>
       </c>
       <c r="B2761" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2761" s="0" t="s">
-        <v>6665</v>
+        <v>10354</v>
       </c>
       <c r="E2761" s="0" t="s">
-        <v>6666</v>
+        <v>10355</v>
       </c>
       <c r="F2761" s="0" t="s">
-        <v>6667</v>
+        <v>10356</v>
       </c>
     </row>
     <row r="2762" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2762" s="0" t="s">
-        <v>10353</v>
+        <v>10357</v>
       </c>
       <c r="B2762" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2762" s="0" t="s">
-        <v>10354</v>
+        <v>6665</v>
       </c>
       <c r="E2762" s="0" t="s">
-        <v>10355</v>
+        <v>6666</v>
       </c>
       <c r="F2762" s="0" t="s">
-        <v>10356</v>
+        <v>6667</v>
       </c>
     </row>
     <row r="2763" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2763" s="0" t="s">
-        <v>10357</v>
+        <v>10358</v>
       </c>
       <c r="B2763" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2763" s="0" t="s">
-        <v>10358</v>
+        <v>10359</v>
       </c>
       <c r="E2763" s="0" t="s">
-        <v>10359</v>
+        <v>10360</v>
       </c>
       <c r="F2763" s="0" t="s">
-        <v>10360</v>
+        <v>10361</v>
       </c>
     </row>
     <row r="2764" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2764" s="0" t="s">
-        <v>10361</v>
+        <v>10362</v>
       </c>
       <c r="B2764" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2764" s="0" t="s">
-        <v>10362</v>
+        <v>10363</v>
       </c>
       <c r="E2764" s="0" t="s">
-        <v>10363</v>
+        <v>10364</v>
       </c>
       <c r="F2764" s="0" t="s">
-        <v>10364</v>
+        <v>10365</v>
       </c>
     </row>
     <row r="2765" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2765" s="0" t="s">
-        <v>10365</v>
+        <v>10366</v>
       </c>
       <c r="B2765" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2765" s="0" t="s">
-        <v>10366</v>
+        <v>10367</v>
       </c>
       <c r="E2765" s="0" t="s">
-        <v>10367</v>
+        <v>10368</v>
       </c>
       <c r="F2765" s="0" t="s">
-        <v>10368</v>
+        <v>10369</v>
       </c>
     </row>
     <row r="2766" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2766" s="0" t="s">
-        <v>10369</v>
+        <v>10370</v>
       </c>
       <c r="B2766" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2766" s="0" t="s">
-        <v>10370</v>
+        <v>10371</v>
       </c>
       <c r="E2766" s="0" t="s">
-        <v>10371</v>
+        <v>10372</v>
       </c>
       <c r="F2766" s="0" t="s">
-        <v>10372</v>
+        <v>10373</v>
       </c>
     </row>
     <row r="2767" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2767" s="0" t="s">
-        <v>10373</v>
+        <v>10374</v>
       </c>
       <c r="B2767" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2767" s="0" t="s">
-        <v>10374</v>
+        <v>10375</v>
       </c>
       <c r="E2767" s="0" t="s">
-        <v>10375</v>
+        <v>10376</v>
       </c>
       <c r="F2767" s="0" t="s">
-        <v>10376</v>
+        <v>10377</v>
       </c>
     </row>
     <row r="2768" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2768" s="0" t="s">
-        <v>10377</v>
+        <v>10378</v>
       </c>
       <c r="B2768" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2768" s="0" t="s">
-        <v>10378</v>
+        <v>10379</v>
       </c>
       <c r="E2768" s="0" t="s">
-        <v>10378</v>
+        <v>10380</v>
       </c>
       <c r="F2768" s="0" t="s">
-        <v>10378</v>
+        <v>10381</v>
       </c>
     </row>
     <row r="2769" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2769" s="0" t="s">
-        <v>10379</v>
+        <v>10382</v>
       </c>
       <c r="B2769" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2769" s="0" t="s">
-        <v>10380</v>
+        <v>10383</v>
       </c>
       <c r="E2769" s="0" t="s">
-        <v>10381</v>
+        <v>10383</v>
       </c>
       <c r="F2769" s="0" t="s">
-        <v>10382</v>
+        <v>10383</v>
       </c>
     </row>
     <row r="2770" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2770" s="0" t="s">
-        <v>10383</v>
+        <v>10384</v>
       </c>
       <c r="B2770" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2770" s="0" t="s">
-        <v>10384</v>
+        <v>10385</v>
       </c>
       <c r="E2770" s="0" t="s">
-        <v>10385</v>
+        <v>10386</v>
       </c>
       <c r="F2770" s="0" t="s">
-        <v>10386</v>
+        <v>10387</v>
       </c>
     </row>
     <row r="2771" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2771" s="0" t="s">
-        <v>10387</v>
+        <v>10388</v>
       </c>
       <c r="B2771" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2771" s="0" t="s">
-        <v>10388</v>
+        <v>10389</v>
       </c>
       <c r="E2771" s="0" t="s">
-        <v>10389</v>
+        <v>10390</v>
       </c>
       <c r="F2771" s="0" t="s">
-        <v>10390</v>
+        <v>10391</v>
       </c>
     </row>
     <row r="2772" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2772" s="0" t="s">
-        <v>10391</v>
+        <v>10392</v>
       </c>
       <c r="B2772" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2772" s="0" t="s">
-        <v>10392</v>
+        <v>10393</v>
       </c>
       <c r="E2772" s="0" t="s">
-        <v>10393</v>
+        <v>10394</v>
       </c>
       <c r="F2772" s="0" t="s">
-        <v>10394</v>
+        <v>10395</v>
       </c>
     </row>
     <row r="2773" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2773" s="0" t="s">
-        <v>10395</v>
+        <v>10396</v>
       </c>
       <c r="B2773" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2773" s="0" t="s">
-        <v>10396</v>
+        <v>10397</v>
       </c>
       <c r="E2773" s="0" t="s">
-        <v>10397</v>
+        <v>10398</v>
       </c>
       <c r="F2773" s="0" t="s">
-        <v>10398</v>
+        <v>10399</v>
       </c>
     </row>
     <row r="2774" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2774" s="0" t="s">
-        <v>10399</v>
+        <v>10400</v>
       </c>
       <c r="B2774" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2774" s="0" t="s">
-        <v>10400</v>
+        <v>10401</v>
       </c>
       <c r="E2774" s="0" t="s">
-        <v>10401</v>
+        <v>10402</v>
       </c>
       <c r="F2774" s="0" t="s">
-        <v>10402</v>
+        <v>10403</v>
       </c>
     </row>
     <row r="2775" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2775" s="0" t="s">
-        <v>10403</v>
+        <v>10404</v>
       </c>
       <c r="B2775" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2775" s="0" t="s">
-        <v>10404</v>
+        <v>10405</v>
       </c>
       <c r="E2775" s="0" t="s">
-        <v>10405</v>
+        <v>10406</v>
       </c>
       <c r="F2775" s="0" t="s">
-        <v>10406</v>
+        <v>10407</v>
       </c>
     </row>
     <row r="2776" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2776" s="0" t="s">
-        <v>10407</v>
+        <v>10408</v>
       </c>
       <c r="B2776" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2776" s="0" t="s">
-        <v>10408</v>
+        <v>10409</v>
       </c>
       <c r="E2776" s="0" t="s">
-        <v>10409</v>
+        <v>10410</v>
       </c>
       <c r="F2776" s="0" t="s">
-        <v>10410</v>
+        <v>10411</v>
       </c>
     </row>
     <row r="2777" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2777" s="0" t="s">
-        <v>10411</v>
+        <v>10412</v>
       </c>
       <c r="B2777" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2777" s="0" t="s">
-        <v>10412</v>
+        <v>10413</v>
       </c>
       <c r="E2777" s="0" t="s">
-        <v>10413</v>
+        <v>10414</v>
       </c>
       <c r="F2777" s="0" t="s">
-        <v>10414</v>
+        <v>10415</v>
       </c>
     </row>
     <row r="2778" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2778" s="0" t="s">
-        <v>10415</v>
+        <v>10416</v>
       </c>
       <c r="B2778" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2778" s="0" t="s">
-        <v>10416</v>
+        <v>10417</v>
       </c>
       <c r="E2778" s="0" t="s">
-        <v>10417</v>
+        <v>10418</v>
       </c>
       <c r="F2778" s="0" t="s">
-        <v>10418</v>
+        <v>10419</v>
       </c>
     </row>
     <row r="2779" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2779" s="0" t="s">
-        <v>10419</v>
+        <v>10420</v>
       </c>
       <c r="B2779" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2779" s="0" t="s">
-        <v>10420</v>
+        <v>10421</v>
       </c>
       <c r="E2779" s="0" t="s">
-        <v>10421</v>
+        <v>10422</v>
       </c>
       <c r="F2779" s="0" t="s">
-        <v>10422</v>
+        <v>10423</v>
       </c>
     </row>
     <row r="2780" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2780" s="0" t="s">
-        <v>10423</v>
+        <v>10424</v>
       </c>
       <c r="B2780" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2780" s="0" t="s">
-        <v>10424</v>
+        <v>10425</v>
       </c>
       <c r="E2780" s="0" t="s">
-        <v>10425</v>
+        <v>10426</v>
       </c>
       <c r="F2780" s="0" t="s">
-        <v>10426</v>
+        <v>10427</v>
       </c>
     </row>
     <row r="2781" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2781" s="0" t="s">
-        <v>10427</v>
+        <v>10428</v>
       </c>
       <c r="B2781" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2781" s="0" t="s">
-        <v>10428</v>
+        <v>10429</v>
       </c>
       <c r="E2781" s="0" t="s">
-        <v>10429</v>
+        <v>10430</v>
       </c>
       <c r="F2781" s="0" t="s">
-        <v>10430</v>
+        <v>10431</v>
       </c>
     </row>
     <row r="2782" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2782" s="0" t="s">
-        <v>10431</v>
+        <v>10432</v>
       </c>
       <c r="B2782" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2782" s="0" t="s">
-        <v>10432</v>
+        <v>10433</v>
       </c>
       <c r="E2782" s="0" t="s">
-        <v>10433</v>
+        <v>10434</v>
       </c>
       <c r="F2782" s="0" t="s">
-        <v>10434</v>
+        <v>10435</v>
       </c>
     </row>
     <row r="2783" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2783" s="0" t="s">
-        <v>10435</v>
+        <v>10436</v>
       </c>
       <c r="B2783" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2783" s="0" t="s">
-        <v>10436</v>
+        <v>10437</v>
       </c>
       <c r="E2783" s="0" t="s">
-        <v>10437</v>
+        <v>10438</v>
       </c>
       <c r="F2783" s="0" t="s">
-        <v>10438</v>
+        <v>10439</v>
       </c>
     </row>
     <row r="2784" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2784" s="0" t="s">
-        <v>10439</v>
+        <v>10440</v>
       </c>
       <c r="B2784" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2784" s="0" t="s">
-        <v>10440</v>
+        <v>10441</v>
       </c>
       <c r="E2784" s="0" t="s">
-        <v>10441</v>
+        <v>10442</v>
       </c>
       <c r="F2784" s="0" t="s">
-        <v>10442</v>
+        <v>10443</v>
       </c>
     </row>
     <row r="2785" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2785" s="0" t="s">
-        <v>10443</v>
+        <v>10444</v>
       </c>
       <c r="B2785" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2785" s="0" t="s">
-        <v>10444</v>
+        <v>10445</v>
       </c>
       <c r="E2785" s="0" t="s">
-        <v>10445</v>
+        <v>10446</v>
       </c>
       <c r="F2785" s="0" t="s">
-        <v>10446</v>
+        <v>10447</v>
       </c>
     </row>
     <row r="2786" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2786" s="0" t="s">
-        <v>10447</v>
+        <v>10448</v>
       </c>
       <c r="B2786" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2786" s="0" t="s">
-        <v>10448</v>
+        <v>10449</v>
       </c>
       <c r="E2786" s="0" t="s">
-        <v>10449</v>
+        <v>10450</v>
       </c>
       <c r="F2786" s="0" t="s">
-        <v>10450</v>
+        <v>10451</v>
       </c>
     </row>
     <row r="2787" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2787" s="0" t="s">
-        <v>10451</v>
+        <v>10452</v>
       </c>
       <c r="B2787" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2787" s="0" t="s">
-        <v>10452</v>
+        <v>10453</v>
       </c>
       <c r="E2787" s="0" t="s">
-        <v>10453</v>
+        <v>10454</v>
       </c>
       <c r="F2787" s="0" t="s">
-        <v>10454</v>
+        <v>10455</v>
       </c>
     </row>
     <row r="2788" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2788" s="0" t="s">
-        <v>10455</v>
+        <v>10456</v>
       </c>
       <c r="B2788" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2788" s="0" t="s">
-        <v>10456</v>
+        <v>10457</v>
       </c>
       <c r="E2788" s="0" t="s">
-        <v>10457</v>
+        <v>10458</v>
       </c>
       <c r="F2788" s="0" t="s">
-        <v>10458</v>
+        <v>10459</v>
       </c>
     </row>
     <row r="2789" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2789" s="0" t="s">
-        <v>10459</v>
+        <v>10460</v>
       </c>
       <c r="B2789" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2789" s="0" t="s">
-        <v>10460</v>
+        <v>10461</v>
       </c>
       <c r="E2789" s="0" t="s">
-        <v>10461</v>
+        <v>10462</v>
       </c>
       <c r="F2789" s="0" t="s">
-        <v>10462</v>
+        <v>10463</v>
       </c>
     </row>
     <row r="2790" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2790" s="0" t="s">
-        <v>10463</v>
+        <v>10464</v>
       </c>
       <c r="B2790" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2790" s="0" t="s">
-        <v>10464</v>
+        <v>10465</v>
       </c>
       <c r="E2790" s="0" t="s">
-        <v>10465</v>
+        <v>10466</v>
       </c>
       <c r="F2790" s="0" t="s">
-        <v>10466</v>
+        <v>10467</v>
       </c>
     </row>
     <row r="2791" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2791" s="0" t="s">
-        <v>10467</v>
+        <v>10468</v>
       </c>
       <c r="B2791" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2791" s="0" t="s">
-        <v>10468</v>
+        <v>10469</v>
       </c>
       <c r="E2791" s="0" t="s">
-        <v>10469</v>
+        <v>10470</v>
       </c>
       <c r="F2791" s="0" t="s">
-        <v>10470</v>
+        <v>10471</v>
       </c>
     </row>
     <row r="2792" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2792" s="0" t="s">
-        <v>10471</v>
+        <v>10472</v>
       </c>
       <c r="B2792" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2792" s="0" t="s">
-        <v>10472</v>
+        <v>10473</v>
       </c>
       <c r="E2792" s="0" t="s">
-        <v>10473</v>
+        <v>10474</v>
       </c>
       <c r="F2792" s="0" t="s">
-        <v>10474</v>
+        <v>10475</v>
       </c>
     </row>
     <row r="2793" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2793" s="0" t="s">
-        <v>10475</v>
+        <v>10476</v>
       </c>
       <c r="B2793" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2793" s="0" t="s">
-        <v>10476</v>
+        <v>10477</v>
       </c>
       <c r="E2793" s="0" t="s">
-        <v>10477</v>
+        <v>10478</v>
       </c>
       <c r="F2793" s="0" t="s">
-        <v>10478</v>
+        <v>10479</v>
       </c>
     </row>
     <row r="2794" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2794" s="0" t="s">
-        <v>10479</v>
+        <v>10480</v>
       </c>
       <c r="B2794" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2794" s="0" t="s">
-        <v>10480</v>
+        <v>10481</v>
       </c>
       <c r="E2794" s="0" t="s">
-        <v>10481</v>
+        <v>10482</v>
       </c>
       <c r="F2794" s="0" t="s">
-        <v>10482</v>
+        <v>10483</v>
       </c>
     </row>
     <row r="2795" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2795" s="0" t="s">
-        <v>10483</v>
+        <v>10484</v>
       </c>
       <c r="B2795" s="0" t="s">
         <v>3054</v>
       </c>
       <c r="D2795" s="0" t="s">
-        <v>10484</v>
+        <v>10485</v>
       </c>
       <c r="E2795" s="0" t="s">
+        <v>10486</v>
+      </c>
+      <c r="F2795" s="0" t="s">
+        <v>10487</v>
+      </c>
+    </row>
+    <row r="2796" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2796" s="0" t="s">
+        <v>10488</v>
+      </c>
+      <c r="B2796" s="0" t="s">
+        <v>3054</v>
+      </c>
+      <c r="D2796" s="0" t="s">
+        <v>10489</v>
+      </c>
+      <c r="E2796" s="0" t="s">
         <v>6198</v>
       </c>
-      <c r="F2795" s="0" t="s">
-        <v>10485</v>
+      <c r="F2796" s="0" t="s">
+        <v>10490</v>
       </c>
     </row>
   </sheetData>
